--- a/outputs/остатки_себес_по_брендам_площадки.xlsx
+++ b/outputs/остатки_себес_по_брендам_площадки.xlsx
@@ -79,7 +79,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -94,6 +94,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00005BFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -138,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,14 +155,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -166,18 +172,21 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -544,28 +553,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ДАШБОРД — ОСТАТКИ И СЕБЕС ПО БРЕНДАМ + ПЛОЩАДКА ПРОДАЖИ</t>
+          <t>ДАШБОРД — ОСТАТКИ, СЕБЕС ПО БРЕНДАМ, ПЛОЩАДКА</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Площадка: OZON — Round Lab, Celimax, VT, Medicube, Derma Factory, Skin1004. Остальные — WB.</t>
+          <t>OZON: Round Lab, Celimax, VT, Medicube, Derma Factory, Skin1004. Остальные — WB. 15 000 Celimax тонер и 15 000 Round Lab пенка — в Бишкеке (вычтено).</t>
         </is>
       </c>
     </row>
@@ -592,10 +602,15 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Итого шт</t>
+          <t>Бишкек</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Итого РФ шт</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
@@ -616,13 +631,16 @@
         <v>25113</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>35071</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>60184</v>
+        <v>20071</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>15000</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>48038177</v>
+        <v>45184</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>34718177</v>
       </c>
     </row>
     <row r="6">
@@ -640,13 +658,16 @@
         <v>4579</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>28400</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>32979</v>
+        <v>13400</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>15000</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>19546609</v>
+        <v>17979</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>10966609</v>
       </c>
     </row>
     <row r="7">
@@ -667,9 +688,12 @@
         <v>7095</v>
       </c>
       <c r="E7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6" t="n">
         <v>7095</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="6" t="n">
         <v>3360330</v>
       </c>
     </row>
@@ -691,9 +715,12 @@
         <v>3320</v>
       </c>
       <c r="E8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="n">
         <v>3369</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="6" t="n">
         <v>2796558</v>
       </c>
     </row>
@@ -715,9 +742,12 @@
         <v>1584</v>
       </c>
       <c r="E9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6" t="n">
         <v>2854</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="6" t="n">
         <v>2032612</v>
       </c>
     </row>
@@ -739,9 +769,12 @@
         <v>1620</v>
       </c>
       <c r="E10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="n">
         <v>1620</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="6" t="n">
         <v>1790360</v>
       </c>
     </row>
@@ -751,7 +784,7 @@
           <t>FARMSTAY</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>WB</t>
         </is>
@@ -763,9 +796,12 @@
         <v>0</v>
       </c>
       <c r="E11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6" t="n">
         <v>16591</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="6" t="n">
         <v>7218588</v>
       </c>
     </row>
@@ -775,7 +811,7 @@
           <t>JIGOTT</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>WB</t>
         </is>
@@ -787,9 +823,12 @@
         <v>0</v>
       </c>
       <c r="E12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6" t="n">
         <v>12545</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="6" t="n">
         <v>3585183</v>
       </c>
     </row>
@@ -799,7 +838,7 @@
           <t>MANYO</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>WB</t>
         </is>
@@ -811,9 +850,12 @@
         <v>600</v>
       </c>
       <c r="E13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6" t="n">
         <v>3911</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="6" t="n">
         <v>3277444</v>
       </c>
     </row>
@@ -823,7 +865,7 @@
           <t>ETUDE</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>WB</t>
         </is>
@@ -835,9 +877,12 @@
         <v>0</v>
       </c>
       <c r="E14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="6" t="n">
         <v>6962</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="6" t="n">
         <v>2931002</v>
       </c>
     </row>
@@ -847,7 +892,7 @@
           <t>ENOUGH</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>WB</t>
         </is>
@@ -859,9 +904,12 @@
         <v>0</v>
       </c>
       <c r="E15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="6" t="n">
         <v>9755</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="6" t="n">
         <v>2474366</v>
       </c>
     </row>
@@ -871,7 +919,7 @@
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>WB</t>
         </is>
@@ -883,9 +931,12 @@
         <v>0</v>
       </c>
       <c r="E16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6" t="n">
         <v>4696</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="6" t="n">
         <v>2063109</v>
       </c>
     </row>
@@ -895,7 +946,7 @@
           <t>JMSOLUTION</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>WB</t>
         </is>
@@ -907,9 +958,12 @@
         <v>0</v>
       </c>
       <c r="E17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="6" t="n">
         <v>1487</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="6" t="n">
         <v>777701</v>
       </c>
     </row>
@@ -919,7 +973,7 @@
           <t>HEIMISH</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>WB</t>
         </is>
@@ -931,9 +985,12 @@
         <v>0</v>
       </c>
       <c r="E18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="6" t="n">
         <v>836</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="G18" s="6" t="n">
         <v>693880</v>
       </c>
     </row>
@@ -943,7 +1000,7 @@
           <t>SOME BY MI</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>WB</t>
         </is>
@@ -955,9 +1012,12 @@
         <v>0</v>
       </c>
       <c r="E19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6" t="n">
         <v>580</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="6" t="n">
         <v>381685</v>
       </c>
     </row>
@@ -967,7 +1027,7 @@
           <t>DEOPROCE</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>WB</t>
         </is>
@@ -979,9 +1039,12 @@
         <v>0</v>
       </c>
       <c r="E20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6" t="n">
         <v>699</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="6" t="n">
         <v>356786</v>
       </c>
     </row>
@@ -991,7 +1054,7 @@
           <t>ELIZAVECCA</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>WB</t>
         </is>
@@ -1003,9 +1066,12 @@
         <v>0</v>
       </c>
       <c r="E21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="6" t="n">
         <v>369</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="G21" s="6" t="n">
         <v>121738</v>
       </c>
     </row>
@@ -1015,7 +1081,7 @@
           <t>THE ORDINARY</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>WB</t>
         </is>
@@ -1027,9 +1093,12 @@
         <v>0</v>
       </c>
       <c r="E22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="G22" s="6" t="n">
         <v>96915</v>
       </c>
     </row>
@@ -1039,7 +1108,7 @@
           <t>MASIL</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>WB</t>
         </is>
@@ -1051,9 +1120,12 @@
         <v>0</v>
       </c>
       <c r="E23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="6" t="n">
         <v>103</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="G23" s="6" t="n">
         <v>75087</v>
       </c>
     </row>
@@ -1063,7 +1135,7 @@
           <t>COSRX</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>WB</t>
         </is>
@@ -1075,9 +1147,12 @@
         <v>0</v>
       </c>
       <c r="E24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="6" t="n">
         <v>185</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="G24" s="6" t="n">
         <v>74740</v>
       </c>
     </row>
@@ -1087,7 +1162,7 @@
           <t>LEBELAGE</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>WB</t>
         </is>
@@ -1099,9 +1174,12 @@
         <v>0</v>
       </c>
       <c r="E25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="6" t="n">
         <v>350</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="G25" s="6" t="n">
         <v>58800</v>
       </c>
     </row>
@@ -1111,7 +1189,7 @@
           <t>LANEIGE</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>WB</t>
         </is>
@@ -1123,30 +1201,36 @@
         <v>0</v>
       </c>
       <c r="E26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="6" t="n">
         <v>170</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="G26" s="6" t="n">
         <v>32470</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B27" s="9" t="n"/>
-      <c r="C27" s="10" t="n">
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="11" t="n">
         <v>89770</v>
       </c>
-      <c r="D27" s="10" t="n">
-        <v>77690</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>167460</v>
-      </c>
-      <c r="F27" s="10" t="n">
-        <v>101784140</v>
+      <c r="D27" s="11" t="n">
+        <v>47690</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>137460</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>79884140</v>
       </c>
     </row>
   </sheetData>
@@ -1160,143 +1244,154 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>JMSOLUTION — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>В пути</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Итого шт</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Бишкек</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Итого РФ</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr"/>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr"/>
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>214977901</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>JMSOLUTION - MASK PACK BLACK [30ml*10ea] - ассорти набор 10шт в упаковке</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>523</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="15" t="n">
         <v>815</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="14" t="n">
+      <c r="F4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n">
         <v>815</v>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="I4" s="15" t="n">
         <v>426245</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr"/>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr"/>
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>214964091</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>JMSOLUTION - MASK PACK DISNEY [30ml*10ea]  - ассорти набор из 10шт</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="15" t="n">
         <v>523</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="15" t="n">
         <v>672</v>
       </c>
-      <c r="F5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="14" t="n">
+      <c r="F5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="15" t="n"/>
+      <c r="H5" s="15" t="n">
         <v>672</v>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="I5" s="15" t="n">
         <v>351456</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n"/>
-      <c r="B6" s="15" t="n"/>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="A6" s="16" t="n"/>
+      <c r="B6" s="16" t="n"/>
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n"/>
-      <c r="E6" s="17" t="n">
+      <c r="D6" s="16" t="n"/>
+      <c r="E6" s="18" t="n">
         <v>1487</v>
       </c>
-      <c r="F6" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="17" t="n">
+      <c r="F6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="18" t="n">
         <v>1487</v>
       </c>
-      <c r="H6" s="17" t="n">
+      <c r="I6" s="18" t="n">
         <v>777701</v>
       </c>
     </row>
@@ -1311,119 +1406,129 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>LEBELAGE — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>В пути</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Итого шт</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Бишкек</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Итого РФ</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>8809445616553</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>210575566</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>168</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="15" t="n">
         <v>350</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="14" t="n">
+      <c r="F4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n">
         <v>350</v>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="I4" s="15" t="n">
         <v>58800</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n"/>
-      <c r="B5" s="15" t="n"/>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="A5" s="16" t="n"/>
+      <c r="B5" s="16" t="n"/>
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="17" t="n">
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="18" t="n">
         <v>350</v>
       </c>
-      <c r="F5" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="17" t="n">
+      <c r="F5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="18" t="n">
         <v>350</v>
       </c>
-      <c r="H5" s="17" t="n">
+      <c r="I5" s="18" t="n">
         <v>58800</v>
       </c>
     </row>
@@ -1438,115 +1543,125 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>LANEIGE — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>В пути</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Итого шт</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Бишкек</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Итого РФ</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr"/>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr"/>
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>868761530</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>LANEIGE LIP SLEEPING MASK-BERRY [3g]</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>191</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="15" t="n">
         <v>170</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="14" t="n">
+      <c r="F4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n">
         <v>170</v>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="I4" s="15" t="n">
         <v>32470</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n"/>
-      <c r="B5" s="15" t="n"/>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="A5" s="16" t="n"/>
+      <c r="B5" s="16" t="n"/>
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="17" t="n">
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="18" t="n">
         <v>170</v>
       </c>
-      <c r="F5" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="17" t="n">
+      <c r="F5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="18" t="n">
         <v>170</v>
       </c>
-      <c r="H5" s="17" t="n">
+      <c r="I5" s="18" t="n">
         <v>32470</v>
       </c>
     </row>
@@ -1561,307 +1676,323 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>MANYO — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>В пути</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Итого шт</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Бишкек</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Итого РФ</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>8809657114700</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>198147185</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>960</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="15" t="n">
         <v>1165</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="14" t="n">
+      <c r="F4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n">
         <v>1165</v>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="I4" s="15" t="n">
         <v>1118400</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>8809730957705</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>868700077</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml] / Сыворотка с микроиглами и пробиотиками</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="15" t="n">
         <v>1057</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="15" t="n">
         <v>592</v>
       </c>
-      <c r="F5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="14" t="n">
+      <c r="F5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="15" t="n"/>
+      <c r="H5" s="15" t="n">
         <v>592</v>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="I5" s="15" t="n">
         <v>625744</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>8809730952014</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>198156472</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="15" t="n">
         <v>707</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="15" t="n">
         <v>547</v>
       </c>
-      <c r="F6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="14" t="n">
+      <c r="F6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="15" t="n">
         <v>547</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="I6" s="15" t="n">
         <v>386729</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>8809567929722</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>868575374</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
         </is>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="15" t="n">
         <v>800</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="15" t="n">
         <v>446</v>
       </c>
-      <c r="F7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="14" t="n">
+      <c r="F7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="15" t="n">
         <v>446</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="I7" s="15" t="n">
         <v>356800</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>8809730952236</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>198143251</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>MANYO - Bifida Biome Ampoule Lotion [300ml] / Укрепляющий лосьон с бифидобактериями</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="15" t="n">
         <v>795</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="15" t="n">
         <v>429</v>
       </c>
-      <c r="F8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="14" t="n">
+      <c r="F8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="15" t="n"/>
+      <c r="H8" s="15" t="n">
         <v>429</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="I8" s="15" t="n">
         <v>341055</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>8809730950881</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr"/>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr"/>
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>BIFIDA BIOME AMPOULE TONER 210ml</t>
         </is>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="15" t="n">
         <v>547</v>
       </c>
-      <c r="E9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="14" t="n">
+      <c r="E9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="15" t="n">
         <v>600</v>
       </c>
-      <c r="G9" s="14" t="n">
+      <c r="G9" s="15" t="n"/>
+      <c r="H9" s="15" t="n">
         <v>600</v>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="I9" s="15" t="n">
         <v>328200</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>8809082392292</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>198156698</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="15" t="n">
         <v>913</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="15" t="n">
         <v>132</v>
       </c>
-      <c r="F10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="14" t="n">
+      <c r="F10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="15" t="n">
         <v>132</v>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="I10" s="15" t="n">
         <v>120516</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="n"/>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="A11" s="16" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="17" t="n">
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="18" t="n">
         <v>3311</v>
       </c>
-      <c r="F11" s="17" t="n">
+      <c r="F11" s="18" t="n">
         <v>600</v>
       </c>
-      <c r="G11" s="17" t="n">
+      <c r="G11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="18" t="n">
         <v>3911</v>
       </c>
-      <c r="H11" s="17" t="n">
+      <c r="I11" s="18" t="n">
         <v>3277444</v>
       </c>
     </row>
@@ -1876,119 +2007,129 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>MASIL — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>В пути</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Итого шт</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Бишкек</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Итого РФ</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>8809744060125</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>183030830</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>MASIL - 8 Seconds Salon Hair Mask 350ml Set [350ml+8ml*2]</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>729</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="15" t="n">
         <v>103</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="14" t="n">
+      <c r="F4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n">
         <v>103</v>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="I4" s="15" t="n">
         <v>75087</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n"/>
-      <c r="B5" s="15" t="n"/>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="A5" s="16" t="n"/>
+      <c r="B5" s="16" t="n"/>
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="17" t="n">
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="18" t="n">
         <v>103</v>
       </c>
-      <c r="F5" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="17" t="n">
+      <c r="F5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="18" t="n">
         <v>103</v>
       </c>
-      <c r="H5" s="17" t="n">
+      <c r="I5" s="18" t="n">
         <v>75087</v>
       </c>
     </row>
@@ -2003,671 +2144,699 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>PETITFEE — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>В пути</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Итого шт</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Бишкек</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Итого РФ</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>8809508850443</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>226115324</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs] / Охлаждающая гидрогелевая маска для лица с экстрактом агавы</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>546</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="15" t="n">
         <v>498</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="14" t="n">
+      <c r="F4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n">
         <v>498</v>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="I4" s="15" t="n">
         <v>271908</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>8809239800458</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>179611231</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>PETITFEE - Collagen &amp; CoQ10 Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с коллагеном и коэнзимом Q10</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="15" t="n">
         <v>445</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="15" t="n">
         <v>504</v>
       </c>
-      <c r="F5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="14" t="n">
+      <c r="F5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="15" t="n"/>
+      <c r="H5" s="15" t="n">
         <v>504</v>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="I5" s="15" t="n">
         <v>224280</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>8809508850504</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>180988755</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="15" t="n">
         <v>547</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="15" t="n">
         <v>380</v>
       </c>
-      <c r="F6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="14" t="n">
+      <c r="F6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="15" t="n">
         <v>380</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="I6" s="15" t="n">
         <v>207860</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>4626999886126</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>226114935</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом</t>
         </is>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="15" t="n">
         <v>567</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="15" t="n">
         <v>330</v>
       </c>
-      <c r="F7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="14" t="n">
+      <c r="F7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="15" t="n">
         <v>330</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="I7" s="15" t="n">
         <v>187110</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>8809508850672</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>226115248</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs] / Тонизирующая гидрогелевая маска для лица с экстрактом какао</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="15" t="n">
         <v>557</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="15" t="n">
         <v>258</v>
       </c>
-      <c r="F8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="14" t="n">
+      <c r="F8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="15" t="n"/>
+      <c r="H8" s="15" t="n">
         <v>258</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="I8" s="15" t="n">
         <v>143706</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>8809508850511</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>226114831</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs] / Смягчающая гидрогелевая маска для лица с экстрактом артишока</t>
         </is>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="15" t="n">
         <v>559</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="15" t="n">
         <v>248</v>
       </c>
-      <c r="F9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="14" t="n">
+      <c r="F9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="15" t="n"/>
+      <c r="H9" s="15" t="n">
         <v>248</v>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="I9" s="15" t="n">
         <v>138632</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>4626999886010</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>226115141</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом и экстрактом улитки</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="15" t="n">
         <v>538</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="15" t="n">
         <v>239</v>
       </c>
-      <c r="F10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="14" t="n">
+      <c r="F10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="15" t="n">
         <v>239</v>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="I10" s="15" t="n">
         <v>128582</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>8809239803596</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>180711104</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>PETITFEE - Gold Hydrogel Eye Patch [60ea] / гидрогелевые патчи для глаз с золотом</t>
         </is>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="15" t="n">
         <v>475</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="15" t="n">
         <v>261</v>
       </c>
-      <c r="F11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="14" t="n">
+      <c r="F11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="15" t="n"/>
+      <c r="H11" s="15" t="n">
         <v>261</v>
       </c>
-      <c r="H11" s="14" t="n">
+      <c r="I11" s="15" t="n">
         <v>123975</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>8809508850498</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>180987509</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>PETITFEE - Pink Vita Brightening Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
         </is>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="15" t="n">
         <v>547</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="15" t="n">
         <v>190</v>
       </c>
-      <c r="F12" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="14" t="n">
+      <c r="F12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="15" t="n"/>
+      <c r="H12" s="15" t="n">
         <v>190</v>
       </c>
-      <c r="H12" s="14" t="n">
+      <c r="I12" s="15" t="n">
         <v>103930</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>4626999886003</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>226115478</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с черным жемчугом и золотом</t>
         </is>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="15" t="n">
         <v>538</v>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="15" t="n">
         <v>167</v>
       </c>
-      <c r="F13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="14" t="n">
+      <c r="F13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="15" t="n"/>
+      <c r="H13" s="15" t="n">
         <v>167</v>
       </c>
-      <c r="H13" s="14" t="n">
+      <c r="I13" s="15" t="n">
         <v>89846</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>8809239802872</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>179611207</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>PETITFEE - Gold &amp; Snail Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с золотом и улиткой</t>
         </is>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="15" t="n">
         <v>475</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="15" t="n">
         <v>186</v>
       </c>
-      <c r="F14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="14" t="n">
+      <c r="F14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="15" t="n"/>
+      <c r="H14" s="15" t="n">
         <v>186</v>
       </c>
-      <c r="H14" s="14" t="n">
+      <c r="I14" s="15" t="n">
         <v>88350</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>8809239801820</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>151175880</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с черным жемчугом и золотом</t>
         </is>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="15" t="n">
         <v>448</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="15" t="n">
         <v>169</v>
       </c>
-      <c r="F15" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="14" t="n">
+      <c r="F15" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="15" t="n"/>
+      <c r="H15" s="15" t="n">
         <v>169</v>
       </c>
-      <c r="H15" s="14" t="n">
+      <c r="I15" s="15" t="n">
         <v>75712</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>8809508850696</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>179611304</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea] / Тонизирующие гидрогелевые патчи для глаз с экстрактом какао</t>
         </is>
       </c>
-      <c r="D16" s="14" t="n">
+      <c r="D16" s="15" t="n">
         <v>475</v>
       </c>
-      <c r="E16" s="14" t="n">
+      <c r="E16" s="15" t="n">
         <v>141</v>
       </c>
-      <c r="F16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="14" t="n">
+      <c r="F16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="15" t="n"/>
+      <c r="H16" s="15" t="n">
         <v>141</v>
       </c>
-      <c r="H16" s="14" t="n">
+      <c r="I16" s="15" t="n">
         <v>66975</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>8809508850429</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>151175877</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea] / Охлаждающие гидрогелевые патчи для глаз с экстрактом агавы</t>
         </is>
       </c>
-      <c r="D17" s="14" t="n">
+      <c r="D17" s="15" t="n">
         <v>475</v>
       </c>
-      <c r="E17" s="14" t="n">
+      <c r="E17" s="15" t="n">
         <v>131</v>
       </c>
-      <c r="F17" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="14" t="n">
+      <c r="F17" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="15" t="n"/>
+      <c r="H17" s="15" t="n">
         <v>131</v>
       </c>
-      <c r="H17" s="14" t="n">
+      <c r="I17" s="15" t="n">
         <v>62225</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr"/>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr"/>
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>1175175447</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>PETITFEE - MASK 6 (блек, агава, какао, артишок, голд, ромашка)</t>
         </is>
       </c>
-      <c r="D18" s="14" t="n">
+      <c r="D18" s="15" t="n">
         <v>653</v>
       </c>
-      <c r="E18" s="14" t="n">
+      <c r="E18" s="15" t="n">
         <v>86</v>
       </c>
-      <c r="F18" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="14" t="n">
+      <c r="F18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="15" t="n"/>
+      <c r="H18" s="15" t="n">
         <v>86</v>
       </c>
-      <c r="H18" s="14" t="n">
+      <c r="I18" s="15" t="n">
         <v>56158</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr"/>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr"/>
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>1177994944</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>PETITFEE - MASK 5 (блек, агава, какао, артишок, голд снейл)</t>
         </is>
       </c>
-      <c r="D19" s="14" t="n">
+      <c r="D19" s="15" t="n">
         <v>548</v>
       </c>
-      <c r="E19" s="14" t="n">
+      <c r="E19" s="15" t="n">
         <v>100</v>
       </c>
-      <c r="F19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="14" t="n">
+      <c r="F19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="15" t="n"/>
+      <c r="H19" s="15" t="n">
         <v>100</v>
       </c>
-      <c r="H19" s="14" t="n">
+      <c r="I19" s="15" t="n">
         <v>54800</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>8809508850801</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>180992464</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
         </is>
       </c>
-      <c r="D20" s="14" t="n">
+      <c r="D20" s="15" t="n">
         <v>651</v>
       </c>
-      <c r="E20" s="14" t="n">
+      <c r="E20" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="F20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="14" t="n">
+      <c r="F20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="15" t="n"/>
+      <c r="H20" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="H20" s="14" t="n">
+      <c r="I20" s="15" t="n">
         <v>39060</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>8809508850503</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr"/>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr"/>
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [1 pairs]/ Гидрогелевые патчи для глаз с черным жемчугом и золотом 1 пара</t>
         </is>
       </c>
-      <c r="D21" s="19" t="n"/>
-      <c r="E21" s="19" t="n">
+      <c r="D21" s="20" t="n"/>
+      <c r="E21" s="20" t="n">
         <v>320</v>
       </c>
-      <c r="F21" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="19" t="n">
+      <c r="F21" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="15" t="n"/>
+      <c r="H21" s="20" t="n">
         <v>320</v>
       </c>
-      <c r="H21" s="19" t="n"/>
+      <c r="I21" s="20" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>8809508850597</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr"/>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr"/>
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>PETITFEE - Gold Hydrogel Eye Patch [1 Pairs] / гидрогелевые патчи для глаз с золотом 1 пара</t>
         </is>
       </c>
-      <c r="D22" s="19" t="n"/>
-      <c r="E22" s="19" t="n">
+      <c r="D22" s="20" t="n"/>
+      <c r="E22" s="20" t="n">
         <v>428</v>
       </c>
-      <c r="F22" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="19" t="n">
+      <c r="F22" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="15" t="n"/>
+      <c r="H22" s="20" t="n">
         <v>428</v>
       </c>
-      <c r="H22" s="19" t="n"/>
+      <c r="I22" s="20" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="n"/>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="A23" s="16" t="n"/>
+      <c r="B23" s="16" t="n"/>
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="17" t="n">
+      <c r="D23" s="16" t="n"/>
+      <c r="E23" s="18" t="n">
         <v>4696</v>
       </c>
-      <c r="F23" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="17" t="n">
+      <c r="F23" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="18" t="n">
         <v>4696</v>
       </c>
-      <c r="H23" s="17" t="n">
+      <c r="I23" s="18" t="n">
         <v>2063109</v>
       </c>
     </row>
@@ -2682,436 +2851,459 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>ROUND LAB — площадка: OZON</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="21" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="21" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="21" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="21" t="inlineStr">
+      <c r="F3" s="22" t="inlineStr">
         <is>
           <t>В пути</t>
         </is>
       </c>
-      <c r="G3" s="21" t="inlineStr">
-        <is>
-          <t>Итого шт</t>
-        </is>
-      </c>
-      <c r="H3" s="21" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
+        <is>
+          <t>Бишкек</t>
+        </is>
+      </c>
+      <c r="H3" s="22" t="inlineStr">
+        <is>
+          <t>Итого РФ</t>
+        </is>
+      </c>
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>8809738608364</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>437154709</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>572</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="15" t="n">
         <v>2799</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>25020</v>
-      </c>
-      <c r="G4" s="14" t="n">
-        <v>27819</v>
-      </c>
-      <c r="H4" s="14" t="n">
-        <v>15912468</v>
+      <c r="F4" s="15" t="n">
+        <v>10020</v>
+      </c>
+      <c r="G4" s="23" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H4" s="15" t="n">
+        <v>12819</v>
+      </c>
+      <c r="I4" s="15" t="n">
+        <v>7332468</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>8809738593080</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>437242640</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка для умывания лица от прыщей и акне</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="15" t="n">
         <v>572</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="15" t="n">
         <v>1188</v>
       </c>
-      <c r="F5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="14" t="n">
+      <c r="F5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="15" t="n"/>
+      <c r="H5" s="15" t="n">
         <v>1188</v>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="I5" s="15" t="n">
         <v>679536</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>8809657114731</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr"/>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr"/>
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="15" t="n">
         <v>684</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="15" t="n">
         <v>559</v>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="15" t="n">
         <v>360</v>
       </c>
-      <c r="G6" s="14" t="n">
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="15" t="n">
         <v>919</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="I6" s="15" t="n">
         <v>628596</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>8809962541840</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr"/>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr"/>
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>ROUND LAB CAMELLIA DEEP COLLAGEN FIRMING CREAM_50ml</t>
         </is>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="15" t="n">
         <v>1056</v>
       </c>
-      <c r="E7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="14" t="n">
+      <c r="E7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="15" t="n">
         <v>400</v>
       </c>
-      <c r="G7" s="14" t="n">
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="15" t="n">
         <v>400</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="I7" s="15" t="n">
         <v>422400</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>8809738599044</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr"/>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr"/>
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>1025 DOKDO BUBBLE FOAM_150ml</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="15" t="n">
         <v>655</v>
       </c>
-      <c r="E8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="14" t="n">
+      <c r="E8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="15" t="n">
         <v>600</v>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="G8" s="15" t="n"/>
+      <c r="H8" s="15" t="n">
         <v>600</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="I8" s="15" t="n">
         <v>393000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>8809864754126</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr"/>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr"/>
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>PINE CALMING CICA CLEANSER_150ml</t>
         </is>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="15" t="n">
         <v>591</v>
       </c>
-      <c r="E9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="14" t="n">
+      <c r="E9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="15" t="n">
         <v>600</v>
       </c>
-      <c r="G9" s="14" t="n">
+      <c r="G9" s="15" t="n"/>
+      <c r="H9" s="15" t="n">
         <v>600</v>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="I9" s="15" t="n">
         <v>354600</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>8809849802408</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr"/>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr"/>
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>PINE CALMING CICA BODY WASH_400ml</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="15" t="n">
         <v>691</v>
       </c>
-      <c r="E10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="14" t="n">
+      <c r="E10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="15" t="n">
         <v>400</v>
       </c>
-      <c r="G10" s="14" t="n">
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="15" t="n">
         <v>400</v>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="I10" s="15" t="n">
         <v>276400</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>8809750462708</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr"/>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr"/>
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>PINE CALMING CICA PAD_50pcs</t>
         </is>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="15" t="n">
         <v>892</v>
       </c>
-      <c r="E11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="14" t="n">
+      <c r="E11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="15" t="n">
         <v>270</v>
       </c>
-      <c r="G11" s="14" t="n">
+      <c r="G11" s="15" t="n"/>
+      <c r="H11" s="15" t="n">
         <v>270</v>
       </c>
-      <c r="H11" s="14" t="n">
+      <c r="I11" s="15" t="n">
         <v>240840</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>8809962542137</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr"/>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr"/>
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>PINE CALMING CICA CREAM PLUS_60ml</t>
         </is>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="15" t="n">
         <v>992</v>
       </c>
-      <c r="E12" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="14" t="n">
+      <c r="E12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="15" t="n">
         <v>240</v>
       </c>
-      <c r="G12" s="14" t="n">
+      <c r="G12" s="15" t="n"/>
+      <c r="H12" s="15" t="n">
         <v>240</v>
       </c>
-      <c r="H12" s="14" t="n">
+      <c r="I12" s="15" t="n">
         <v>238080</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>8809738593240</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr"/>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr"/>
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>SOYBEAN SERUM_50ml</t>
         </is>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="15" t="n">
         <v>934</v>
       </c>
-      <c r="E13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="14" t="n">
+      <c r="E13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="15" t="n">
         <v>210</v>
       </c>
-      <c r="G13" s="14" t="n">
+      <c r="G13" s="15" t="n"/>
+      <c r="H13" s="15" t="n">
         <v>210</v>
       </c>
-      <c r="H13" s="14" t="n">
+      <c r="I13" s="15" t="n">
         <v>196140</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>8809962540553</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr"/>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr"/>
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>ROUND LAB STICK POUCH KIT</t>
         </is>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="15" t="n">
         <v>555</v>
       </c>
-      <c r="E14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="14" t="n">
+      <c r="E14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="15" t="n">
         <v>300</v>
       </c>
-      <c r="G14" s="14" t="n">
+      <c r="G14" s="15" t="n"/>
+      <c r="H14" s="15" t="n">
         <v>300</v>
       </c>
-      <c r="H14" s="14" t="n">
+      <c r="I14" s="15" t="n">
         <v>166500</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>8809738600221</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>437190353</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем  с березовым соком</t>
         </is>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="15" t="n">
         <v>1153</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="15" t="n">
         <v>33</v>
       </c>
-      <c r="F15" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="14" t="n">
+      <c r="F15" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="15" t="n"/>
+      <c r="H15" s="15" t="n">
         <v>33</v>
       </c>
-      <c r="H15" s="14" t="n">
+      <c r="I15" s="15" t="n">
         <v>38049</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="n"/>
-      <c r="B16" s="15" t="n"/>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="A16" s="16" t="n"/>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="17" t="n">
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="18" t="n">
         <v>4579</v>
       </c>
-      <c r="F16" s="17" t="n">
-        <v>28400</v>
-      </c>
-      <c r="G16" s="17" t="n">
-        <v>32979</v>
-      </c>
-      <c r="H16" s="17" t="n">
-        <v>19546609</v>
+      <c r="F16" s="18" t="n">
+        <v>13400</v>
+      </c>
+      <c r="G16" s="18" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H16" s="18" t="n">
+        <v>17979</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>10966609</v>
       </c>
     </row>
   </sheetData>
@@ -3125,235 +3317,249 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>SKIN1004 — площадка: OZON</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="21" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="21" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="21" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="21" t="inlineStr">
+      <c r="F3" s="22" t="inlineStr">
         <is>
           <t>В пути</t>
         </is>
       </c>
-      <c r="G3" s="21" t="inlineStr">
-        <is>
-          <t>Итого шт</t>
-        </is>
-      </c>
-      <c r="H3" s="21" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
+        <is>
+          <t>Бишкек</t>
+        </is>
+      </c>
+      <c r="H3" s="22" t="inlineStr">
+        <is>
+          <t>Итого РФ</t>
+        </is>
+      </c>
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>8809576260601</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr"/>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr"/>
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>SKIN1004 Madagascar Centella Ampoule 55ml</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>734</v>
       </c>
-      <c r="E4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="14" t="n">
+      <c r="E4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="15" t="n">
         <v>1500</v>
       </c>
-      <c r="G4" s="14" t="n">
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n">
         <v>1500</v>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="I4" s="15" t="n">
         <v>1101000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>8809576261134</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr"/>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr"/>
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>SKIN1004 Madagascar Centella Soothing Cream 75ml</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="15" t="n">
         <v>917</v>
       </c>
-      <c r="E5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="14" t="n">
+      <c r="E5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="15" t="n">
         <v>920</v>
       </c>
-      <c r="G5" s="14" t="n">
+      <c r="G5" s="15" t="n"/>
+      <c r="H5" s="15" t="n">
         <v>920</v>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="I5" s="15" t="n">
         <v>843640</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>8809576261172</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr"/>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr"/>
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>SKIN1004 Madagascar Centella Tone Brightening Capsule Ampoule 100ml</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="15" t="n">
         <v>925</v>
       </c>
-      <c r="E6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="14" t="n">
+      <c r="E6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="15" t="n">
         <v>900</v>
       </c>
-      <c r="G6" s="14" t="n">
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="15" t="n">
         <v>900</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="I6" s="15" t="n">
         <v>832500</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>8809576260618</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>214311963</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
         </is>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="15" t="n">
         <v>428</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="F7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="14" t="n">
+      <c r="F7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="I7" s="15" t="n">
         <v>11984</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>8809576260724</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>214312149</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>SKIN1004 - Madagascar Centella Hyalu-Cica Sleeping Pack [30ml] / Увлажняющая гиалуроновая ночная маска для сухой кожи</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="15" t="n">
         <v>354</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="F8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="14" t="n">
+      <c r="F8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="15" t="n"/>
+      <c r="H8" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="I8" s="15" t="n">
         <v>7434</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n"/>
-      <c r="B9" s="15" t="n"/>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="A9" s="16" t="n"/>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="17" t="n">
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="18" t="n">
         <v>49</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="18" t="n">
         <v>3320</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="18" t="n">
         <v>3369</v>
       </c>
-      <c r="H9" s="17" t="n">
+      <c r="I9" s="18" t="n">
         <v>2796558</v>
       </c>
     </row>
@@ -3368,147 +3574,158 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>SOME BY MI — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>В пути</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Итого шт</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Бишкек</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Итого РФ</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>8809408260793</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>248928046</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cleansing Bar [106g] / Мыло для проблемной кожи с aha bha кислотами</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>610</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="15" t="n">
         <v>525</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="14" t="n">
+      <c r="F4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n">
         <v>525</v>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="I4" s="15" t="n">
         <v>320250</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr"/>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr"/>
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>248929125</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] /  Крем для лица</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="15" t="n">
         <v>1117</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="15" t="n">
         <v>55</v>
       </c>
-      <c r="F5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="14" t="n">
+      <c r="F5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="15" t="n"/>
+      <c r="H5" s="15" t="n">
         <v>55</v>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="I5" s="15" t="n">
         <v>61435</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n"/>
-      <c r="B6" s="15" t="n"/>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="A6" s="16" t="n"/>
+      <c r="B6" s="16" t="n"/>
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n"/>
-      <c r="E6" s="17" t="n">
+      <c r="D6" s="16" t="n"/>
+      <c r="E6" s="18" t="n">
         <v>580</v>
       </c>
-      <c r="F6" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="17" t="n">
+      <c r="F6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="18" t="n">
         <v>580</v>
       </c>
-      <c r="H6" s="17" t="n">
+      <c r="I6" s="18" t="n">
         <v>381685</v>
       </c>
     </row>
@@ -3523,151 +3740,162 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>THE ORDINARY — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>В пути</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Итого шт</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Бишкек</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Итого РФ</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>769915190946</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>214312385</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>THE ORDINARY - Argireline Solution 10% [30ml] / Сыворотка для лица от прыщей и акне с ниацинамидом 10 %</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>782</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="15" t="n">
         <v>95</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="14" t="n">
+      <c r="F4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n">
         <v>95</v>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="I4" s="15" t="n">
         <v>74290</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>769915196498</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>247275092</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="15" t="n">
         <v>905</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="F5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="14" t="n">
+      <c r="F5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="15" t="n"/>
+      <c r="H5" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="I5" s="15" t="n">
         <v>22625</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n"/>
-      <c r="B6" s="15" t="n"/>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="A6" s="16" t="n"/>
+      <c r="B6" s="16" t="n"/>
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n"/>
-      <c r="E6" s="17" t="n">
+      <c r="D6" s="16" t="n"/>
+      <c r="E6" s="18" t="n">
         <v>120</v>
       </c>
-      <c r="F6" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="17" t="n">
+      <c r="F6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="18" t="n">
         <v>120</v>
       </c>
-      <c r="H6" s="17" t="n">
+      <c r="I6" s="18" t="n">
         <v>96915</v>
       </c>
     </row>
@@ -3682,119 +3910,129 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>COSRX — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>В пути</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Итого шт</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Бишкек</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Итого РФ</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>8809416471112</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>204258828</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>COSRX - Salicylic Acid Daily Gentle Cleanser [150ml] / Пенка с салициловой кислотой для проблемной кожи</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>404</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="15" t="n">
         <v>185</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="14" t="n">
+      <c r="F4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n">
         <v>185</v>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="I4" s="15" t="n">
         <v>74740</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n"/>
-      <c r="B5" s="15" t="n"/>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="A5" s="16" t="n"/>
+      <c r="B5" s="16" t="n"/>
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="17" t="n">
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="18" t="n">
         <v>185</v>
       </c>
-      <c r="F5" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="17" t="n">
+      <c r="F5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="18" t="n">
         <v>185</v>
       </c>
-      <c r="H5" s="17" t="n">
+      <c r="I5" s="18" t="n">
         <v>74740</v>
       </c>
     </row>
@@ -3809,884 +4047,922 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>CELIMAX — площадка: OZON</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="21" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="21" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="21" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="21" t="inlineStr">
+      <c r="F3" s="22" t="inlineStr">
         <is>
           <t>В пути</t>
         </is>
       </c>
-      <c r="G3" s="21" t="inlineStr">
-        <is>
-          <t>Итого шт</t>
-        </is>
-      </c>
-      <c r="H3" s="21" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
+        <is>
+          <t>Бишкек</t>
+        </is>
+      </c>
+      <c r="H3" s="22" t="inlineStr">
+        <is>
+          <t>Итого РФ</t>
+        </is>
+      </c>
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>8809606850475</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>868516027</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>Celimax Dual Barrier Creamy Toner, тонер 150 мл</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>888</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="15" t="n">
         <v>13908</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>25008</v>
-      </c>
-      <c r="G4" s="14" t="n">
-        <v>38916</v>
-      </c>
-      <c r="H4" s="14" t="n">
-        <v>34557408</v>
+      <c r="F4" s="15" t="n">
+        <v>10008</v>
+      </c>
+      <c r="G4" s="23" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H4" s="15" t="n">
+        <v>23916</v>
+      </c>
+      <c r="I4" s="15" t="n">
+        <v>21237408</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>8809700320812</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>551387355</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]/Подтягивающий бустер-крем с ретинолом для лица</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="15" t="n">
         <v>572</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="15" t="n">
         <v>5658</v>
       </c>
-      <c r="F5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="14" t="n">
+      <c r="F5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="15" t="n"/>
+      <c r="H5" s="15" t="n">
         <v>5658</v>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="I5" s="15" t="n">
         <v>3236376</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>8809783321225</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>551607905</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="15" t="n">
         <v>768</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="15" t="n">
         <v>1432</v>
       </c>
-      <c r="F6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="14" t="n">
+      <c r="F6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="15" t="n">
         <v>1432</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="I6" s="15" t="n">
         <v>1099776</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>8809782557861</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr"/>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr"/>
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL CICA SOOTHING CREAM 50ML</t>
         </is>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="15" t="n">
         <v>732</v>
       </c>
-      <c r="E7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="14" t="n">
+      <c r="E7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="15" t="n">
         <v>1200</v>
       </c>
-      <c r="G7" s="14" t="n">
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="15" t="n">
         <v>1200</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="I7" s="15" t="n">
         <v>878400</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>8809743546323</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>551540924</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="15" t="n">
         <v>616</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="15" t="n">
         <v>1362</v>
       </c>
-      <c r="F8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="14" t="n">
+      <c r="F8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="15" t="n"/>
+      <c r="H8" s="15" t="n">
         <v>1362</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="I8" s="15" t="n">
         <v>838992</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>8809463992615</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr"/>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr"/>
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>CELIMAX JI WOO GAE HEARTLEAF BHA PEELING PAD 60PADS</t>
         </is>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="15" t="n">
         <v>672</v>
       </c>
-      <c r="E9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="14" t="n">
+      <c r="E9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="15" t="n">
         <v>1200</v>
       </c>
-      <c r="G9" s="14" t="n">
+      <c r="G9" s="15" t="n"/>
+      <c r="H9" s="15" t="n">
         <v>1200</v>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="I9" s="15" t="n">
         <v>806400</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>8809743544626</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr"/>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr"/>
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL CICA NIACINAMIDE AC CALMING SERUM 40ML</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="15" t="n">
         <v>886</v>
       </c>
-      <c r="E10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="14" t="n">
+      <c r="E10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="15" t="n">
         <v>864</v>
       </c>
-      <c r="G10" s="14" t="n">
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="15" t="n">
         <v>864</v>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="I10" s="15" t="n">
         <v>765504</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>8809750465464</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr"/>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr"/>
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL NONI CALMING GLOW PAD 50EA</t>
         </is>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="15" t="n">
         <v>771</v>
       </c>
-      <c r="E11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="14" t="n">
+      <c r="E11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="15" t="n">
         <v>984</v>
       </c>
-      <c r="G11" s="14" t="n">
+      <c r="G11" s="15" t="n"/>
+      <c r="H11" s="15" t="n">
         <v>984</v>
       </c>
-      <c r="H11" s="14" t="n">
+      <c r="I11" s="15" t="n">
         <v>758664</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>8809700320805</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>551465879</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинолом и микроиглами для лица</t>
         </is>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="15" t="n">
         <v>592</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="15" t="n">
         <v>1255</v>
       </c>
-      <c r="F12" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="14" t="n">
+      <c r="F12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="15" t="n"/>
+      <c r="H12" s="15" t="n">
         <v>1255</v>
       </c>
-      <c r="H12" s="14" t="n">
+      <c r="I12" s="15" t="n">
         <v>742960</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>8809686386185</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr"/>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr"/>
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL NONI ENERGY REPAIR CREAM 50ML</t>
         </is>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="15" t="n">
         <v>1020</v>
       </c>
-      <c r="E13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="14" t="n">
+      <c r="E13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="15" t="n">
         <v>720</v>
       </c>
-      <c r="G13" s="14" t="n">
+      <c r="G13" s="15" t="n"/>
+      <c r="H13" s="15" t="n">
         <v>720</v>
       </c>
-      <c r="H13" s="14" t="n">
+      <c r="I13" s="15" t="n">
         <v>734400</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>8809743546880</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr"/>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr"/>
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>CELIMAX OIL CONTROL MOISTURIZING CREAM 80ML</t>
         </is>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="15" t="n">
         <v>848</v>
       </c>
-      <c r="E14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="14" t="n">
+      <c r="E14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="15" t="n">
         <v>600</v>
       </c>
-      <c r="G14" s="14" t="n">
+      <c r="G14" s="15" t="n"/>
+      <c r="H14" s="15" t="n">
         <v>600</v>
       </c>
-      <c r="H14" s="14" t="n">
+      <c r="I14" s="15" t="n">
         <v>508800</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>8800296551789</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr"/>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr"/>
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>CELIMAX PORE+DARK SPOT BRIGHTENING KIT</t>
         </is>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="15" t="n">
         <v>590</v>
       </c>
-      <c r="E15" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="14" t="n">
+      <c r="E15" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="15" t="n">
         <v>576</v>
       </c>
-      <c r="G15" s="14" t="n">
+      <c r="G15" s="15" t="n"/>
+      <c r="H15" s="15" t="n">
         <v>576</v>
       </c>
-      <c r="H15" s="14" t="n">
+      <c r="I15" s="15" t="n">
         <v>339840</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>8809971482349</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr"/>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr"/>
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL NONI STARTER KIT</t>
         </is>
       </c>
-      <c r="D16" s="14" t="n">
+      <c r="D16" s="15" t="n">
         <v>692</v>
       </c>
-      <c r="E16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="14" t="n">
+      <c r="E16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="15" t="n">
         <v>480</v>
       </c>
-      <c r="G16" s="14" t="n">
+      <c r="G16" s="15" t="n"/>
+      <c r="H16" s="15" t="n">
         <v>480</v>
       </c>
-      <c r="H16" s="14" t="n">
+      <c r="I16" s="15" t="n">
         <v>332160</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>8809463992707</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr"/>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr"/>
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>CELIMAX ONE STEP BODY BRIGHTENING PAD 60PADS</t>
         </is>
       </c>
-      <c r="D17" s="14" t="n">
+      <c r="D17" s="15" t="n">
         <v>567</v>
       </c>
-      <c r="E17" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="14" t="n">
+      <c r="E17" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="15" t="n">
         <v>528</v>
       </c>
-      <c r="G17" s="14" t="n">
+      <c r="G17" s="15" t="n"/>
+      <c r="H17" s="15" t="n">
         <v>528</v>
       </c>
-      <c r="H17" s="14" t="n">
+      <c r="I17" s="15" t="n">
         <v>299376</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>8809626564000</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr"/>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr"/>
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>CELIMAX DERMA NATURE GLUTATHIONE LONGLASTING TONE-UP CREAM 35ML</t>
         </is>
       </c>
-      <c r="D18" s="14" t="n">
+      <c r="D18" s="15" t="n">
         <v>592</v>
       </c>
-      <c r="E18" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="14" t="n">
+      <c r="E18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="15" t="n">
         <v>468</v>
       </c>
-      <c r="G18" s="14" t="n">
+      <c r="G18" s="15" t="n"/>
+      <c r="H18" s="15" t="n">
         <v>468</v>
       </c>
-      <c r="H18" s="14" t="n">
+      <c r="I18" s="15" t="n">
         <v>277056</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>8809954940354</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr"/>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr"/>
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL NONI REFRESH CLAY MASK 120G</t>
         </is>
       </c>
-      <c r="D19" s="14" t="n">
+      <c r="D19" s="15" t="n">
         <v>610</v>
       </c>
-      <c r="E19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="14" t="n">
+      <c r="E19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="15" t="n">
         <v>408</v>
       </c>
-      <c r="G19" s="14" t="n">
+      <c r="G19" s="15" t="n"/>
+      <c r="H19" s="15" t="n">
         <v>408</v>
       </c>
-      <c r="H19" s="14" t="n">
+      <c r="I19" s="15" t="n">
         <v>248880</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>8809606852332</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr"/>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr"/>
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>CELIMAX DUAL BARRIER TRIAL KIT</t>
         </is>
       </c>
-      <c r="D20" s="14" t="n">
+      <c r="D20" s="15" t="n">
         <v>509</v>
       </c>
-      <c r="E20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="14" t="n">
+      <c r="E20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="15" t="n">
         <v>448</v>
       </c>
-      <c r="G20" s="14" t="n">
+      <c r="G20" s="15" t="n"/>
+      <c r="H20" s="15" t="n">
         <v>448</v>
       </c>
-      <c r="H20" s="14" t="n">
+      <c r="I20" s="15" t="n">
         <v>228032</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>8809463993889</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr"/>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr"/>
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>CELIMAX JI WOO GAE ONE STEP MILD CLEANSING PAD 60PADS</t>
         </is>
       </c>
-      <c r="D21" s="14" t="n">
+      <c r="D21" s="15" t="n">
         <v>631</v>
       </c>
-      <c r="E21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="14" t="n">
+      <c r="E21" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="15" t="n">
         <v>352</v>
       </c>
-      <c r="G21" s="14" t="n">
+      <c r="G21" s="15" t="n"/>
+      <c r="H21" s="15" t="n">
         <v>352</v>
       </c>
-      <c r="H21" s="14" t="n">
+      <c r="I21" s="15" t="n">
         <v>222112</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>8809606850499</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr"/>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr"/>
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>CELIMAX DUAL BARRIER MILD GEL CLEANSER 200ML</t>
         </is>
       </c>
-      <c r="D22" s="14" t="n">
+      <c r="D22" s="15" t="n">
         <v>727</v>
       </c>
-      <c r="E22" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="14" t="n">
+      <c r="E22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="15" t="n">
         <v>288</v>
       </c>
-      <c r="G22" s="14" t="n">
+      <c r="G22" s="15" t="n"/>
+      <c r="H22" s="15" t="n">
         <v>288</v>
       </c>
-      <c r="H22" s="14" t="n">
+      <c r="I22" s="15" t="n">
         <v>209376</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>8806050298525</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr"/>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr"/>
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>CELIMAX DERMA NATURE FRESH BLACKHEAD JOJOBA CLEANSING OIL 150ML</t>
         </is>
       </c>
-      <c r="D23" s="14" t="n">
+      <c r="D23" s="15" t="n">
         <v>651</v>
       </c>
-      <c r="E23" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="14" t="n">
+      <c r="E23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="15" t="n">
         <v>315</v>
       </c>
-      <c r="G23" s="14" t="n">
+      <c r="G23" s="15" t="n"/>
+      <c r="H23" s="15" t="n">
         <v>315</v>
       </c>
-      <c r="H23" s="14" t="n">
+      <c r="I23" s="15" t="n">
         <v>205065</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>8809783323519</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>551600265</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
         </is>
       </c>
-      <c r="D24" s="14" t="n">
+      <c r="D24" s="15" t="n">
         <v>157</v>
       </c>
-      <c r="E24" s="14" t="n">
+      <c r="E24" s="15" t="n">
         <v>1252</v>
       </c>
-      <c r="F24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="14" t="n">
+      <c r="F24" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="15" t="n"/>
+      <c r="H24" s="15" t="n">
         <v>1252</v>
       </c>
-      <c r="H24" s="14" t="n">
+      <c r="I24" s="15" t="n">
         <v>196564</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>8809541379468</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr"/>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr"/>
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL NONI ACNE BUBBLE CLEANSER 155ML</t>
         </is>
       </c>
-      <c r="D25" s="14" t="n">
+      <c r="D25" s="15" t="n">
         <v>605</v>
       </c>
-      <c r="E25" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="14" t="n">
+      <c r="E25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="15" t="n">
         <v>312</v>
       </c>
-      <c r="G25" s="14" t="n">
+      <c r="G25" s="15" t="n"/>
+      <c r="H25" s="15" t="n">
         <v>312</v>
       </c>
-      <c r="H25" s="14" t="n">
+      <c r="I25" s="15" t="n">
         <v>188760</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>8809975194439</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr"/>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr"/>
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>CELIMAX DERMA NATURE RELIEF MADECICA PH BALANCING FOAM CLEANSING 150ML</t>
         </is>
       </c>
-      <c r="D26" s="14" t="n">
+      <c r="D26" s="15" t="n">
         <v>488</v>
       </c>
-      <c r="E26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="14" t="n">
+      <c r="E26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="15" t="n">
         <v>320</v>
       </c>
-      <c r="G26" s="14" t="n">
+      <c r="G26" s="15" t="n"/>
+      <c r="H26" s="15" t="n">
         <v>320</v>
       </c>
-      <c r="H26" s="14" t="n">
+      <c r="I26" s="15" t="n">
         <v>156160</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>8809606850505</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>551392965</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
         </is>
       </c>
-      <c r="D27" s="14" t="n">
+      <c r="D27" s="15" t="n">
         <v>924</v>
       </c>
-      <c r="E27" s="14" t="n">
+      <c r="E27" s="15" t="n">
         <v>112</v>
       </c>
-      <c r="F27" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="14" t="n">
+      <c r="F27" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="15" t="n"/>
+      <c r="H27" s="15" t="n">
         <v>112</v>
       </c>
-      <c r="H27" s="14" t="n">
+      <c r="I27" s="15" t="n">
         <v>103488</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>8809875907412</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>551482493</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]/Сыворотка для выравнивания тона и рельефа кожи лица</t>
         </is>
       </c>
-      <c r="D28" s="14" t="n">
+      <c r="D28" s="15" t="n">
         <v>748</v>
       </c>
-      <c r="E28" s="14" t="n">
+      <c r="E28" s="15" t="n">
         <v>76</v>
       </c>
-      <c r="F28" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="14" t="n">
+      <c r="F28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="15" t="n"/>
+      <c r="H28" s="15" t="n">
         <v>76</v>
       </c>
-      <c r="H28" s="14" t="n">
+      <c r="I28" s="15" t="n">
         <v>56848</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>8809875907795</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>551472457</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]/Восстанавливающая сыворотка с экстрактом нони для лица</t>
         </is>
       </c>
-      <c r="D29" s="14" t="n">
+      <c r="D29" s="15" t="n">
         <v>824</v>
       </c>
-      <c r="E29" s="14" t="n">
+      <c r="E29" s="15" t="n">
         <v>35</v>
       </c>
-      <c r="F29" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="14" t="n">
+      <c r="F29" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="15" t="n"/>
+      <c r="H29" s="15" t="n">
         <v>35</v>
       </c>
-      <c r="H29" s="14" t="n">
+      <c r="I29" s="15" t="n">
         <v>28840</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>8809954940132</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>551518955</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]/Восстанавливающий тонер с экстрактом нони</t>
         </is>
       </c>
-      <c r="D30" s="14" t="n">
+      <c r="D30" s="15" t="n">
         <v>780</v>
       </c>
-      <c r="E30" s="14" t="n">
+      <c r="E30" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="F30" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="14" t="n">
+      <c r="F30" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="15" t="n"/>
+      <c r="H30" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="H30" s="14" t="n">
+      <c r="I30" s="15" t="n">
         <v>17940</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="n"/>
-      <c r="B31" s="15" t="n"/>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="A31" s="16" t="n"/>
+      <c r="B31" s="16" t="n"/>
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D31" s="15" t="n"/>
-      <c r="E31" s="17" t="n">
+      <c r="D31" s="16" t="n"/>
+      <c r="E31" s="18" t="n">
         <v>25113</v>
       </c>
-      <c r="F31" s="17" t="n">
-        <v>35071</v>
-      </c>
-      <c r="G31" s="17" t="n">
-        <v>60184</v>
-      </c>
-      <c r="H31" s="17" t="n">
-        <v>48038177</v>
+      <c r="F31" s="18" t="n">
+        <v>20071</v>
+      </c>
+      <c r="G31" s="18" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H31" s="18" t="n">
+        <v>45184</v>
+      </c>
+      <c r="I31" s="18" t="n">
+        <v>34718177</v>
       </c>
     </row>
   </sheetData>
@@ -4700,203 +4976,216 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>VT COSMETIC — площадка: OZON</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="21" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="21" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="21" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="21" t="inlineStr">
+      <c r="F3" s="22" t="inlineStr">
         <is>
           <t>В пути</t>
         </is>
       </c>
-      <c r="G3" s="21" t="inlineStr">
-        <is>
-          <t>Итого шт</t>
-        </is>
-      </c>
-      <c r="H3" s="21" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
+        <is>
+          <t>Бишкек</t>
+        </is>
+      </c>
+      <c r="H3" s="22" t="inlineStr">
+        <is>
+          <t>Итого РФ</t>
+        </is>
+      </c>
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>8803463004286</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>1119249556</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>1396</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="15" t="n">
         <v>892</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="14" t="n">
+      <c r="F4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n">
         <v>892</v>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="I4" s="15" t="n">
         <v>1245232</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>8803463006501</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr"/>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr"/>
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>VT REEDLE S LIP PLUMPER EXPERT</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="15" t="n">
         <v>751</v>
       </c>
-      <c r="E5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="14" t="n">
+      <c r="E5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="15" t="n">
         <v>528</v>
       </c>
-      <c r="G5" s="14" t="n">
+      <c r="G5" s="15" t="n"/>
+      <c r="H5" s="15" t="n">
         <v>528</v>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="I5" s="15" t="n">
         <v>396528</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>8809695678363</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>1123494802</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="15" t="n">
         <v>1034</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="15" t="n">
         <v>378</v>
       </c>
-      <c r="F6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="14" t="n">
+      <c r="F6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="15" t="n">
         <v>378</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="I6" s="15" t="n">
         <v>390852</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>8809695679544</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr"/>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr"/>
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>VT REEDLE SHOT LIFTING EYE CREAM</t>
         </is>
       </c>
-      <c r="D7" s="19" t="n"/>
-      <c r="E7" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="19" t="n">
+      <c r="D7" s="20" t="n"/>
+      <c r="E7" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="20" t="n">
         <v>1056</v>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="20" t="n">
         <v>1056</v>
       </c>
-      <c r="H7" s="19" t="n"/>
+      <c r="I7" s="20" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n"/>
-      <c r="B8" s="15" t="n"/>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="A8" s="16" t="n"/>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="17" t="n">
+      <c r="D8" s="16" t="n"/>
+      <c r="E8" s="18" t="n">
         <v>1270</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="18" t="n">
         <v>1584</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="18" t="n">
         <v>2854</v>
       </c>
-      <c r="H8" s="17" t="n">
+      <c r="I8" s="18" t="n">
         <v>2032612</v>
       </c>
     </row>
@@ -4911,255 +5200,270 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>MEDICUBE — площадка: OZON</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="21" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="21" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="21" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="21" t="inlineStr">
+      <c r="F3" s="22" t="inlineStr">
         <is>
           <t>В пути</t>
         </is>
       </c>
-      <c r="G3" s="21" t="inlineStr">
-        <is>
-          <t>Итого шт</t>
-        </is>
-      </c>
-      <c r="H3" s="21" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
+        <is>
+          <t>Бишкек</t>
+        </is>
+      </c>
+      <c r="H3" s="22" t="inlineStr">
+        <is>
+          <t>Итого РФ</t>
+        </is>
+      </c>
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>8800256115549</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr"/>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr"/>
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>PDRN PINK EXOSOME SHOT SERUM 7500 30ml</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>1150</v>
       </c>
-      <c r="E4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="14" t="n">
+      <c r="E4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="15" t="n">
         <v>400</v>
       </c>
-      <c r="G4" s="14" t="n">
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n">
         <v>400</v>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="I4" s="15" t="n">
         <v>460000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>8800256115532</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr"/>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr"/>
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>PDRN PINK EXOSOME SHOT SERUM 2000 30ml</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="15" t="n">
         <v>1050</v>
       </c>
-      <c r="E5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="14" t="n">
+      <c r="E5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="15" t="n">
         <v>300</v>
       </c>
-      <c r="G5" s="14" t="n">
+      <c r="G5" s="15" t="n"/>
+      <c r="H5" s="15" t="n">
         <v>300</v>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="I5" s="15" t="n">
         <v>315000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>8800256119660</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr"/>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr"/>
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>TXA NIACINAMIDE CAPSULE CREAM 55g</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="15" t="n">
         <v>1266</v>
       </c>
-      <c r="E6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="14" t="n">
+      <c r="E6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="15" t="n">
         <v>240</v>
       </c>
-      <c r="G6" s="14" t="n">
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="15" t="n">
         <v>240</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="I6" s="15" t="n">
         <v>303840</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>8800256108053</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr"/>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr"/>
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>PDRN PINK PEPTIDE SERUM 30ml</t>
         </is>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="15" t="n">
         <v>942</v>
       </c>
-      <c r="E7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="14" t="n">
+      <c r="E7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="15" t="n">
         <v>320</v>
       </c>
-      <c r="G7" s="14" t="n">
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="15" t="n">
         <v>320</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="I7" s="15" t="n">
         <v>301440</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>8800256118885</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr"/>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr"/>
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>PDRN PINK COLLAGEN CAPSULE CREAM 55g</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="15" t="n">
         <v>1393</v>
       </c>
-      <c r="E8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="14" t="n">
+      <c r="E8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="15" t="n">
         <v>160</v>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="G8" s="15" t="n"/>
+      <c r="H8" s="15" t="n">
         <v>160</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="I8" s="15" t="n">
         <v>222880</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>8800256113101</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr"/>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr"/>
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>PDRN PINK HYALURONIC MOISTURIZING CREAM 50ml</t>
         </is>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="15" t="n">
         <v>936</v>
       </c>
-      <c r="E9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="14" t="n">
+      <c r="E9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="15" t="n">
         <v>200</v>
       </c>
-      <c r="G9" s="14" t="n">
+      <c r="G9" s="15" t="n"/>
+      <c r="H9" s="15" t="n">
         <v>200</v>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="I9" s="15" t="n">
         <v>187200</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="A10" s="16" t="n"/>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="17" t="n">
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="18" t="n">
         <v>1620</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="G10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="18" t="n">
         <v>1620</v>
       </c>
-      <c r="H10" s="17" t="n">
+      <c r="I10" s="18" t="n">
         <v>1790360</v>
       </c>
     </row>
@@ -5174,283 +5478,299 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>DERMA FACTORY — площадка: OZON</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="21" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="21" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="21" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="21" t="inlineStr">
+      <c r="F3" s="22" t="inlineStr">
         <is>
           <t>В пути</t>
         </is>
       </c>
-      <c r="G3" s="21" t="inlineStr">
-        <is>
-          <t>Итого шт</t>
-        </is>
-      </c>
-      <c r="H3" s="21" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
+        <is>
+          <t>Бишкек</t>
+        </is>
+      </c>
+      <c r="H3" s="22" t="inlineStr">
+        <is>
+          <t>Итого РФ</t>
+        </is>
+      </c>
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>8809331319360</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr"/>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr"/>
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>[Derma Factory] PDRN 4% Ampoule</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>592</v>
       </c>
-      <c r="E4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="14" t="n">
+      <c r="E4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="15" t="n">
         <v>1530</v>
       </c>
-      <c r="G4" s="14" t="n">
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n">
         <v>1530</v>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="I4" s="15" t="n">
         <v>905760</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>8809563067923</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr"/>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr"/>
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>[Derma Factory] Porphyrin 20% Ampoule stick</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="15" t="n">
         <v>534</v>
       </c>
-      <c r="E5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="14" t="n">
+      <c r="E5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="15" t="n">
         <v>1053</v>
       </c>
-      <c r="G5" s="14" t="n">
+      <c r="G5" s="15" t="n"/>
+      <c r="H5" s="15" t="n">
         <v>1053</v>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="I5" s="15" t="n">
         <v>562302</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>8809563066773</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr"/>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr"/>
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>[Derma Factory] Retinal 300ppm Cream</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="15" t="n">
         <v>443</v>
       </c>
-      <c r="E6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="14" t="n">
+      <c r="E6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="15" t="n">
         <v>1248</v>
       </c>
-      <c r="G6" s="14" t="n">
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="15" t="n">
         <v>1248</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="I6" s="15" t="n">
         <v>552864</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>8809563068258</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr"/>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr"/>
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>[Derma Factory] Tranexamic Acid 6% Cream</t>
         </is>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="15" t="n">
         <v>401</v>
       </c>
-      <c r="E7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="14" t="n">
+      <c r="E7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="15" t="n">
         <v>1344</v>
       </c>
-      <c r="G7" s="14" t="n">
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="15" t="n">
         <v>1344</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="I7" s="15" t="n">
         <v>538944</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>8809563066797</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr"/>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr"/>
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>[Derma Factory] Niacinamide 20% Serum</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="15" t="n">
         <v>289</v>
       </c>
-      <c r="E8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="14" t="n">
+      <c r="E8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="15" t="n">
         <v>1020</v>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="G8" s="15" t="n"/>
+      <c r="H8" s="15" t="n">
         <v>1020</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="I8" s="15" t="n">
         <v>294780</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>8809331317182</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr"/>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr"/>
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>[Derma Factory] Matrixyl 15% + Argireline 2% Serum</t>
         </is>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="15" t="n">
         <v>684</v>
       </c>
-      <c r="E9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="14" t="n">
+      <c r="E9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="15" t="n">
         <v>420</v>
       </c>
-      <c r="G9" s="14" t="n">
+      <c r="G9" s="15" t="n"/>
+      <c r="H9" s="15" t="n">
         <v>420</v>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="I9" s="15" t="n">
         <v>287280</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>8809331313818</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr"/>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr"/>
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>[Derma Factory] Bakuchiol Spicule Cream</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="15" t="n">
         <v>455</v>
       </c>
-      <c r="E10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="14" t="n">
+      <c r="E10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="15" t="n">
         <v>480</v>
       </c>
-      <c r="G10" s="14" t="n">
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="15" t="n">
         <v>480</v>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="I10" s="15" t="n">
         <v>218400</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="n"/>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="A11" s="16" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="17" t="n">
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="18" t="n">
         <v>7095</v>
       </c>
-      <c r="G11" s="17" t="n">
+      <c r="G11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="18" t="n">
         <v>7095</v>
       </c>
-      <c r="H11" s="17" t="n">
+      <c r="I11" s="18" t="n">
         <v>3360330</v>
       </c>
     </row>
@@ -5465,179 +5785,191 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>DEOPROCE — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>В пути</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Итого шт</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Бишкек</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Итого РФ</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr"/>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr"/>
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>214305722</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>DEOPROCE SHAMPOO+BALSAM - BLACK GARLIC[2000ml]</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>787</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="15" t="n">
         <v>352</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="14" t="n">
+      <c r="F4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n">
         <v>352</v>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="I4" s="15" t="n">
         <v>277024</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>8809410033545</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>608841921</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [200ml]/ Шампунь с черным чесноком против выпадения волос</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="15" t="n">
         <v>211</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="15" t="n">
         <v>292</v>
       </c>
-      <c r="F5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="14" t="n">
+      <c r="F5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="15" t="n"/>
+      <c r="H5" s="15" t="n">
         <v>292</v>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="I5" s="15" t="n">
         <v>61612</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>8809975191773</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>608837066</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [600ml] мягкая упаковка Шампунь с черным чесноком против выпадения волос</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="15" t="n">
         <v>330</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="15" t="n">
         <v>55</v>
       </c>
-      <c r="F6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="14" t="n">
+      <c r="F6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="15" t="n">
         <v>55</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="I6" s="15" t="n">
         <v>18150</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n"/>
-      <c r="B7" s="15" t="n"/>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="A7" s="16" t="n"/>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="17" t="n">
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="18" t="n">
         <v>699</v>
       </c>
-      <c r="F7" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="17" t="n">
+      <c r="F7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="18" t="n">
         <v>699</v>
       </c>
-      <c r="H7" s="17" t="n">
+      <c r="I7" s="18" t="n">
         <v>356786</v>
       </c>
     </row>
@@ -5652,151 +5984,162 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>ELIZAVECCA — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>В пути</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Итого шт</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Бишкек</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Итого РФ</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>8809339903523</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>207796350</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>ELIZAVECCA - CER-100 Collagen Ceramide Coating Protein Treatment [100ml] / Коллагеновая маска для волос</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>302</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="15" t="n">
         <v>319</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="14" t="n">
+      <c r="F4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n">
         <v>319</v>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="I4" s="15" t="n">
         <v>96338</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>8809418752400</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>206058262</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>ELIZAVECCA - Hell-Pore Galactomyces Pure Ample / Сыворотка для лица с экстрактом галактомисиса</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="15" t="n">
         <v>508</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="F5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="14" t="n">
+      <c r="F5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="15" t="n"/>
+      <c r="H5" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="I5" s="15" t="n">
         <v>25400</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n"/>
-      <c r="B6" s="15" t="n"/>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="A6" s="16" t="n"/>
+      <c r="B6" s="16" t="n"/>
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n"/>
-      <c r="E6" s="17" t="n">
+      <c r="D6" s="16" t="n"/>
+      <c r="E6" s="18" t="n">
         <v>369</v>
       </c>
-      <c r="F6" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="17" t="n">
+      <c r="F6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="18" t="n">
         <v>369</v>
       </c>
-      <c r="H6" s="17" t="n">
+      <c r="I6" s="18" t="n">
         <v>121738</v>
       </c>
     </row>
@@ -5811,555 +6154,579 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>ENOUGH — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>В пути</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Итого шт</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Бишкек</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Итого РФ</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>8809755463335</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>238415286</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>221</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="15" t="n">
         <v>5314</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="14" t="n">
+      <c r="F4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n">
         <v>5314</v>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="I4" s="15" t="n">
         <v>1174394</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>8809605870993</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>170198835</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>ENOUGH - Premium Ultra X10 Cover Up Collagen Foundation [Tone 13] / Тональный крем с коллагеном 13 тон</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="15" t="n">
         <v>375</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="15" t="n">
         <v>908</v>
       </c>
-      <c r="F5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="14" t="n">
+      <c r="F5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="15" t="n"/>
+      <c r="H5" s="15" t="n">
         <v>908</v>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="I5" s="15" t="n">
         <v>340500</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr"/>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr"/>
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>212889028</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="15" t="n">
         <v>243</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="15" t="n">
         <v>682</v>
       </c>
-      <c r="F6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="14" t="n">
+      <c r="F6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="15" t="n">
         <v>682</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="I6" s="15" t="n">
         <v>165726</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>8809755462116</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>238413828</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>ENOUGH - Collagen Moisture BB Cream SPF47 PA+++ [50ml] / Увлажняющий BB крем с коллагеном</t>
         </is>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="15" t="n">
         <v>249</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="15" t="n">
         <v>664</v>
       </c>
-      <c r="F7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="14" t="n">
+      <c r="F7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="15" t="n">
         <v>664</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="I7" s="15" t="n">
         <v>165336</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>8809474498809</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>207796789</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>ENOUGH - Gold Snail Moisture Foundation [Tone 13] / Тональный крем с муцином улитки 13 тон</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="15" t="n">
         <v>306</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="15" t="n">
         <v>457</v>
       </c>
-      <c r="F8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="14" t="n">
+      <c r="F8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="15" t="n"/>
+      <c r="H8" s="15" t="n">
         <v>457</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="I8" s="15" t="n">
         <v>139842</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>8809605871945</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>170198109</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>ENOUGH - Premium Rich Gold Double Wear Radiance Foundation [Tone 21] / Тональный крем с частичками золота 21 тон</t>
         </is>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="15" t="n">
         <v>330</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="15" t="n">
         <v>338</v>
       </c>
-      <c r="F9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="14" t="n">
+      <c r="F9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="15" t="n"/>
+      <c r="H9" s="15" t="n">
         <v>338</v>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="I9" s="15" t="n">
         <v>111540</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr"/>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr"/>
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>212889027</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="15" t="n">
         <v>243</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="15" t="n">
         <v>454</v>
       </c>
-      <c r="F10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="14" t="n">
+      <c r="F10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="15" t="n">
         <v>454</v>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="I10" s="15" t="n">
         <v>110322</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr"/>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr"/>
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>212889025</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) 4.5 рейтинг</t>
         </is>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="15" t="n">
         <v>243</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="15" t="n">
         <v>289</v>
       </c>
-      <c r="F11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="14" t="n">
+      <c r="F11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="15" t="n"/>
+      <c r="H11" s="15" t="n">
         <v>289</v>
       </c>
-      <c r="H11" s="14" t="n">
+      <c r="I11" s="15" t="n">
         <v>70227</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>8809474498816</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>207796898</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>ENOUGH - Gold Snail Moisture Foundation [Tone 21] / Тональный крем с муцином улитки 21 тон</t>
         </is>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="15" t="n">
         <v>331</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="15" t="n">
         <v>186</v>
       </c>
-      <c r="F12" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="14" t="n">
+      <c r="F12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="15" t="n"/>
+      <c r="H12" s="15" t="n">
         <v>186</v>
       </c>
-      <c r="H12" s="14" t="n">
+      <c r="I12" s="15" t="n">
         <v>61566</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>8809605871938</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>170198180</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>ENOUGH - Premium Rich Gold Double Wear Radiance Foundation [Tone 13] / Тональный крем с частичками золота 13 тон</t>
         </is>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="15" t="n">
         <v>330</v>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="15" t="n">
         <v>133</v>
       </c>
-      <c r="F13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="14" t="n">
+      <c r="F13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="15" t="n"/>
+      <c r="H13" s="15" t="n">
         <v>133</v>
       </c>
-      <c r="H13" s="14" t="n">
+      <c r="I13" s="15" t="n">
         <v>43890</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>8809480652165</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>238416010</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
         </is>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="15" t="n">
         <v>244</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="15" t="n">
         <v>158</v>
       </c>
-      <c r="F14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="14" t="n">
+      <c r="F14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="15" t="n"/>
+      <c r="H14" s="15" t="n">
         <v>158</v>
       </c>
-      <c r="H14" s="14" t="n">
+      <c r="I14" s="15" t="n">
         <v>38552</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>8809280062379</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>150925322</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>ENOUGH - Collagen Moisture Foundation [Tone 21] / Тональный крем для лица с коллагеном 21 тон</t>
         </is>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="15" t="n">
         <v>303</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="15" t="n">
         <v>126</v>
       </c>
-      <c r="F15" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="14" t="n">
+      <c r="F15" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="15" t="n"/>
+      <c r="H15" s="15" t="n">
         <v>126</v>
       </c>
-      <c r="H15" s="14" t="n">
+      <c r="I15" s="15" t="n">
         <v>38178</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>8809605870979</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>170198337</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>ENOUGH - Premium 8 Peptide Full Cover Perfect Foundation [Tone 21] / Тональный крем с пептидами 21 тон</t>
         </is>
       </c>
-      <c r="D16" s="14" t="n">
+      <c r="D16" s="15" t="n">
         <v>365</v>
       </c>
-      <c r="E16" s="14" t="n">
+      <c r="E16" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="F16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="14" t="n">
+      <c r="F16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="15" t="n"/>
+      <c r="H16" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="H16" s="14" t="n">
+      <c r="I16" s="15" t="n">
         <v>6205</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>8809280062362</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>150925321</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>ENOUGH - Collagen Moisture Foundation [Tone 13] / Тональный крем для лица с коллагеном 13 тон</t>
         </is>
       </c>
-      <c r="D17" s="14" t="n">
+      <c r="D17" s="15" t="n">
         <v>276</v>
       </c>
-      <c r="E17" s="14" t="n">
+      <c r="E17" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="F17" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="14" t="n">
+      <c r="F17" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="15" t="n"/>
+      <c r="H17" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="H17" s="14" t="n">
+      <c r="I17" s="15" t="n">
         <v>4692</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>8809474497079</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>151132052</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>ENOUGH - Collagen 3in1 Whitening Moisture Foundation [Tone 21] / Тональный крем для лица с коллагеном 3в1 [21 тон]</t>
         </is>
       </c>
-      <c r="D18" s="14" t="n">
+      <c r="D18" s="15" t="n">
         <v>283</v>
       </c>
-      <c r="E18" s="14" t="n">
+      <c r="E18" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="F18" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="14" t="n">
+      <c r="F18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="15" t="n"/>
+      <c r="H18" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="H18" s="14" t="n">
+      <c r="I18" s="15" t="n">
         <v>3396</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n"/>
-      <c r="B19" s="15" t="n"/>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="A19" s="16" t="n"/>
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="17" t="n">
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="18" t="n">
         <v>9755</v>
       </c>
-      <c r="F19" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="17" t="n">
+      <c r="F19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="18" t="n">
         <v>9755</v>
       </c>
-      <c r="H19" s="17" t="n">
+      <c r="I19" s="18" t="n">
         <v>2474366</v>
       </c>
     </row>
@@ -6374,119 +6741,129 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>ETUDE — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>В пути</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Итого шт</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Бишкек</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Итого РФ</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>8809820683118</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>151313163</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>421</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="15" t="n">
         <v>6962</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="14" t="n">
+      <c r="F4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n">
         <v>6962</v>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="I4" s="15" t="n">
         <v>2931002</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n"/>
-      <c r="B5" s="15" t="n"/>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="A5" s="16" t="n"/>
+      <c r="B5" s="16" t="n"/>
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="17" t="n">
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="18" t="n">
         <v>6962</v>
       </c>
-      <c r="F5" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="17" t="n">
+      <c r="F5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="18" t="n">
         <v>6962</v>
       </c>
-      <c r="H5" s="17" t="n">
+      <c r="I5" s="18" t="n">
         <v>2931002</v>
       </c>
     </row>
@@ -6501,407 +6878,426 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>FARMSTAY — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>В пути</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Итого шт</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Бишкек</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Итого РФ</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>8809469770002</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>168956391</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>408</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="15" t="n">
         <v>5563</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="14" t="n">
+      <c r="F4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n">
         <v>5563</v>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="I4" s="15" t="n">
         <v>2269704</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>8809595053284</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>207475898</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер 2в1 с коллагеном</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="15" t="n">
         <v>457</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="15" t="n">
         <v>3287</v>
       </c>
-      <c r="F5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="14" t="n">
+      <c r="F5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="15" t="n"/>
+      <c r="H5" s="15" t="n">
         <v>3287</v>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="I5" s="15" t="n">
         <v>1502159</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>8809595056384</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>207472742</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="15" t="n">
         <v>457</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="15" t="n">
         <v>3053</v>
       </c>
-      <c r="F6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="14" t="n">
+      <c r="F6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="15" t="n">
         <v>3053</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="I6" s="15" t="n">
         <v>1395221</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>8809595053659</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>207476309</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер с аргановым маслом</t>
         </is>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="15" t="n">
         <v>461</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="15" t="n">
         <v>2187</v>
       </c>
-      <c r="F7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="14" t="n">
+      <c r="F7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="15" t="n">
         <v>2187</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="I7" s="15" t="n">
         <v>1008207</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>8809480770975</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>207469760</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="15" t="n">
         <v>491</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="15" t="n">
         <v>770</v>
       </c>
-      <c r="F8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="14" t="n">
+      <c r="F8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="15" t="n"/>
+      <c r="H8" s="15" t="n">
         <v>770</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="I8" s="15" t="n">
         <v>378070</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>8809469772778</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>419630142</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой </t>
         </is>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="15" t="n">
         <v>450</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="15" t="n">
         <v>623</v>
       </c>
-      <c r="F9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="14" t="n">
+      <c r="F9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="15" t="n"/>
+      <c r="H9" s="15" t="n">
         <v>623</v>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="I9" s="15" t="n">
         <v>280350</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>8809317289274</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>169076150</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="15" t="n">
         <v>374</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="15" t="n">
         <v>512</v>
       </c>
-      <c r="F10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="14" t="n">
+      <c r="F10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="15" t="n">
         <v>512</v>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="I10" s="15" t="n">
         <v>191488</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>8802221001338</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>207477077</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>FARMSTAY - Collagen Water Full Moist Cream [100g] / Увлажняющий крем с коллагеном</t>
         </is>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="15" t="n">
         <v>544</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="15" t="n">
         <v>165</v>
       </c>
-      <c r="F11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="14" t="n">
+      <c r="F11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="15" t="n"/>
+      <c r="H11" s="15" t="n">
         <v>165</v>
       </c>
-      <c r="H11" s="14" t="n">
+      <c r="I11" s="15" t="n">
         <v>89760</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>8809317289472</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>207476777</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания </t>
         </is>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="15" t="n">
         <v>221</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="15" t="n">
         <v>313</v>
       </c>
-      <c r="F12" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="14" t="n">
+      <c r="F12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="15" t="n"/>
+      <c r="H12" s="15" t="n">
         <v>313</v>
       </c>
-      <c r="H12" s="14" t="n">
+      <c r="I12" s="15" t="n">
         <v>69173</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>8809480772504</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>212885914</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml] / Сыворотка роллер для глаз</t>
         </is>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="15" t="n">
         <v>292</v>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="15" t="n">
         <v>118</v>
       </c>
-      <c r="F13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="14" t="n">
+      <c r="F13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="15" t="n"/>
+      <c r="H13" s="15" t="n">
         <v>118</v>
       </c>
-      <c r="H13" s="14" t="n">
+      <c r="I13" s="15" t="n">
         <v>34456</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="n"/>
-      <c r="B14" s="15" t="n"/>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="A14" s="16" t="n"/>
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="17" t="n">
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="18" t="n">
         <v>16591</v>
       </c>
-      <c r="F14" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="17" t="n">
+      <c r="F14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="18" t="n">
         <v>16591</v>
       </c>
-      <c r="H14" s="17" t="n">
+      <c r="I14" s="18" t="n">
         <v>7218588</v>
       </c>
     </row>
@@ -6916,119 +7312,129 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>HEIMISH — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>В пути</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Итого шт</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Бишкек</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Итого РФ</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>8809481760463</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>207466866</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] / База под макияж SPF50+ PA+++</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>830</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="15" t="n">
         <v>836</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="14" t="n">
+      <c r="F4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n">
         <v>836</v>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="I4" s="15" t="n">
         <v>693880</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n"/>
-      <c r="B5" s="15" t="n"/>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="A5" s="16" t="n"/>
+      <c r="B5" s="16" t="n"/>
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="17" t="n">
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="18" t="n">
         <v>836</v>
       </c>
-      <c r="F5" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="17" t="n">
+      <c r="F5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="18" t="n">
         <v>836</v>
       </c>
-      <c r="H5" s="17" t="n">
+      <c r="I5" s="18" t="n">
         <v>693880</v>
       </c>
     </row>
@@ -7043,339 +7449,356 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>JIGOTT — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>В пути</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Итого шт</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Бишкек</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Итого РФ</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>8809210034124</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>207482718</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>262</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="15" t="n">
         <v>6937</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="14" t="n">
+      <c r="F4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n">
         <v>6937</v>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="I4" s="15" t="n">
         <v>1817494</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr"/>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr"/>
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>255574453</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>JIGOTT - Ассорти набор масок [27ml х 15]</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="15" t="n">
         <v>394</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="15" t="n">
         <v>1160</v>
       </c>
-      <c r="F5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="14" t="n">
+      <c r="F5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="15" t="n"/>
+      <c r="H5" s="15" t="n">
         <v>1160</v>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="I5" s="15" t="n">
         <v>457040</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>8809210034087</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>207483780</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>JIGOTT - Birds Nest Firming Cream [70ml] / Антивозрастной крем с экстрактом ласточкиного гнезда</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="15" t="n">
         <v>262</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="15" t="n">
         <v>1485</v>
       </c>
-      <c r="F6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="14" t="n">
+      <c r="F6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="15" t="n">
         <v>1485</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="I6" s="15" t="n">
         <v>389070</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>8809541282447</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>212757456</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
         </is>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="15" t="n">
         <v>325</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="15" t="n">
         <v>1154</v>
       </c>
-      <c r="F7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="14" t="n">
+      <c r="F7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="15" t="n">
         <v>1154</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="I7" s="15" t="n">
         <v>375050</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>8809541282461</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>212760119</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="15" t="n">
         <v>325</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="15" t="n">
         <v>1124</v>
       </c>
-      <c r="F8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="14" t="n">
+      <c r="F8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="15" t="n"/>
+      <c r="H8" s="15" t="n">
         <v>1124</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="I8" s="15" t="n">
         <v>365300</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>8809210036517</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>207483179</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица увлажняющий антивозрастной с муцином улитки</t>
         </is>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="15" t="n">
         <v>246</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="15" t="n">
         <v>524</v>
       </c>
-      <c r="F9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="14" t="n">
+      <c r="F9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="15" t="n"/>
+      <c r="H9" s="15" t="n">
         <v>524</v>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="I9" s="15" t="n">
         <v>128904</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>8809541282485</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>212883090</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>JIGOTT - Aura Secret Hyaluronec Acid Toner [300ml] / Тонер с гиалуроновой кислотой антивозрастной</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="15" t="n">
         <v>325</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="15" t="n">
         <v>92</v>
       </c>
-      <c r="F10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="14" t="n">
+      <c r="F10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="15" t="n">
         <v>92</v>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="I10" s="15" t="n">
         <v>29900</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>8809541282508</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>212759698</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml] / Тонер для лица увлажняющий с экстрактом алоэ</t>
         </is>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="15" t="n">
         <v>325</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="15" t="n">
         <v>69</v>
       </c>
-      <c r="F11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="14" t="n">
+      <c r="F11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="15" t="n"/>
+      <c r="H11" s="15" t="n">
         <v>69</v>
       </c>
-      <c r="H11" s="14" t="n">
+      <c r="I11" s="15" t="n">
         <v>22425</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n"/>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="A12" s="16" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="17" t="n">
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="18" t="n">
         <v>12545</v>
       </c>
-      <c r="F12" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="17" t="n">
+      <c r="F12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="18" t="n">
         <v>12545</v>
       </c>
-      <c r="H12" s="17" t="n">
+      <c r="I12" s="18" t="n">
         <v>3585183</v>
       </c>
     </row>

--- a/outputs/остатки_себес_по_брендам_площадки.xlsx
+++ b/outputs/остатки_себес_по_брендам_площадки.xlsx
@@ -67,11 +67,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="007030A0"/>
-      <sz val="13"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="007030A0"/>
+      <sz val="13"/>
     </font>
     <font>
       <b val="1"/>
@@ -143,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -162,7 +162,10 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -173,8 +176,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -553,29 +556,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ДАШБОРД — ОСТАТКИ, СЕБЕС ПО БРЕНДАМ, ПЛОЩАДКА</t>
+          <t>ДАШБОРД — ПОЛНАЯ КАРТИНА: СКЛАД + ПРИХОД 12.10 (МАШИНА)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>OZON: Round Lab, Celimax, VT, Medicube, Derma Factory, Skin1004. Остальные — WB. 15 000 Celimax тонер и 15 000 Round Lab пенка — в Бишкеке (вычтено).</t>
+          <t>12.10 машина привозит приход (без 15 000 пенки и 15 000 тонера — они в Бишкеке). OZON: Round Lab, Celimax, VT, Medicube, Derma Factory, Skin1004. Остальные — WB.</t>
         </is>
       </c>
     </row>
@@ -597,7 +600,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>В пути</t>
+          <t>Приход 12.10 (машина)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -808,7 +811,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -817,25 +820,25 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>12545</v>
+        <v>3311</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>12545</v>
+        <v>4511</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>3585183</v>
+        <v>3605644</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -844,19 +847,19 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>3311</v>
+        <v>12545</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>3911</v>
+        <v>12545</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>3277444</v>
+        <v>3585183</v>
       </c>
     </row>
     <row r="14">
@@ -1221,16 +1224,54 @@
         <v>89770</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>47690</v>
+        <v>48290</v>
       </c>
       <c r="E27" s="11" t="n">
         <v>30000</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>137460</v>
+        <v>138060</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>79884140</v>
+        <v>80212340</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Итого OZON</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="n">
+        <v>31011</v>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>47090</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>78101</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>55664646</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>Итого WB</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="n">
+        <v>58759</v>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>59959</v>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>24547694</v>
       </c>
     </row>
   </sheetData>
@@ -1252,146 +1293,146 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>JMSOLUTION — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>В пути</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Приход 12.10</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>Бишкек</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>Итого РФ</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr"/>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr"/>
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>214977901</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>JMSOLUTION - MASK PACK BLACK [30ml*10ea] - ассорти набор 10шт в упаковке</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="18" t="n">
         <v>523</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="18" t="n">
         <v>815</v>
       </c>
-      <c r="F4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n">
+      <c r="F4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="n">
         <v>815</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="18" t="n">
         <v>426245</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr"/>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr"/>
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>214964091</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>JMSOLUTION - MASK PACK DISNEY [30ml*10ea]  - ассорти набор из 10шт</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="18" t="n">
         <v>523</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="18" t="n">
         <v>672</v>
       </c>
-      <c r="F5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="15" t="n">
+      <c r="F5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="n">
         <v>672</v>
       </c>
-      <c r="I5" s="15" t="n">
+      <c r="I5" s="18" t="n">
         <v>351456</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n"/>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="A6" s="19" t="n"/>
+      <c r="B6" s="19" t="n"/>
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="18" t="n">
+      <c r="D6" s="19" t="n"/>
+      <c r="E6" s="21" t="n">
         <v>1487</v>
       </c>
-      <c r="F6" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="18" t="n">
+      <c r="F6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="21" t="n">
         <v>1487</v>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="21" t="n">
         <v>777701</v>
       </c>
     </row>
@@ -1414,121 +1455,121 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>LEBELAGE — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>В пути</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Приход 12.10</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>Бишкек</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>Итого РФ</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>8809445616553</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>210575566</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="18" t="n">
         <v>168</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="18" t="n">
         <v>350</v>
       </c>
-      <c r="F4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n">
+      <c r="F4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="n">
         <v>350</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="18" t="n">
         <v>58800</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="A5" s="19" t="n"/>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="18" t="n">
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="21" t="n">
         <v>350</v>
       </c>
-      <c r="F5" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="18" t="n">
+      <c r="F5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="21" t="n">
         <v>350</v>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="I5" s="21" t="n">
         <v>58800</v>
       </c>
     </row>
@@ -1551,117 +1592,117 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>LANEIGE — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>В пути</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Приход 12.10</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>Бишкек</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>Итого РФ</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr"/>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr"/>
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>868761530</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>LANEIGE LIP SLEEPING MASK-BERRY [3g]</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="18" t="n">
         <v>191</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="18" t="n">
         <v>170</v>
       </c>
-      <c r="F4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n">
+      <c r="F4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="n">
         <v>170</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="18" t="n">
         <v>32470</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="A5" s="19" t="n"/>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="18" t="n">
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="21" t="n">
         <v>170</v>
       </c>
-      <c r="F5" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="18" t="n">
+      <c r="F5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="21" t="n">
         <v>170</v>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="I5" s="21" t="n">
         <v>32470</v>
       </c>
     </row>
@@ -1684,316 +1725,316 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>MANYO — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>В пути</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Приход 12.10</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>Бишкек</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>Итого РФ</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>8809657114700</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>198147185</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="18" t="n">
         <v>960</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="18" t="n">
         <v>1165</v>
       </c>
-      <c r="F4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n">
+      <c r="F4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="n">
         <v>1165</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="18" t="n">
         <v>1118400</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>8809730950881</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr"/>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>BIFIDA BIOME AMPOULE TONER 210ml</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="n">
+        <v>547</v>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I5" s="18" t="n">
+        <v>656400</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>8809730957705</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>868700077</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml] / Сыворотка с микроиглами и пробиотиками</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D6" s="18" t="n">
         <v>1057</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E6" s="18" t="n">
         <v>592</v>
       </c>
-      <c r="F5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="15" t="n">
+      <c r="F6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="18" t="n">
         <v>592</v>
       </c>
-      <c r="I5" s="15" t="n">
+      <c r="I6" s="18" t="n">
         <v>625744</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>8809730952014</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>198156472</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D7" s="18" t="n">
         <v>707</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E7" s="18" t="n">
         <v>547</v>
       </c>
-      <c r="F6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="15" t="n">
+      <c r="F7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="18" t="n">
         <v>547</v>
       </c>
-      <c r="I6" s="15" t="n">
+      <c r="I7" s="18" t="n">
         <v>386729</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>8809567929722</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>868575374</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D8" s="18" t="n">
         <v>800</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E8" s="18" t="n">
         <v>446</v>
       </c>
-      <c r="F7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="15" t="n"/>
-      <c r="H7" s="15" t="n">
+      <c r="F8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="18" t="n">
         <v>446</v>
       </c>
-      <c r="I7" s="15" t="n">
+      <c r="I8" s="18" t="n">
         <v>356800</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>8809730952236</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>198143251</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>MANYO - Bifida Biome Ampoule Lotion [300ml] / Укрепляющий лосьон с бифидобактериями</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D9" s="18" t="n">
         <v>795</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E9" s="18" t="n">
         <v>429</v>
       </c>
-      <c r="F8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="15" t="n"/>
-      <c r="H8" s="15" t="n">
+      <c r="F9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="n">
         <v>429</v>
       </c>
-      <c r="I8" s="15" t="n">
+      <c r="I9" s="18" t="n">
         <v>341055</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>8809730950881</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr"/>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>BIFIDA BIOME AMPOULE TONER 210ml</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="n">
-        <v>547</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <v>600</v>
-      </c>
-      <c r="G9" s="15" t="n"/>
-      <c r="H9" s="15" t="n">
-        <v>600</v>
-      </c>
-      <c r="I9" s="15" t="n">
-        <v>328200</v>
-      </c>
-    </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>8809082392292</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>198156698</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
         </is>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="18" t="n">
         <v>913</v>
       </c>
-      <c r="E10" s="15" t="n">
+      <c r="E10" s="18" t="n">
         <v>132</v>
       </c>
-      <c r="F10" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="15" t="n"/>
-      <c r="H10" s="15" t="n">
+      <c r="F10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="18" t="n"/>
+      <c r="H10" s="18" t="n">
         <v>132</v>
       </c>
-      <c r="I10" s="15" t="n">
+      <c r="I10" s="18" t="n">
         <v>120516</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="n"/>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="A11" s="19" t="n"/>
+      <c r="B11" s="19" t="n"/>
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="18" t="n">
+      <c r="D11" s="19" t="n"/>
+      <c r="E11" s="21" t="n">
         <v>3311</v>
       </c>
-      <c r="F11" s="18" t="n">
-        <v>600</v>
-      </c>
-      <c r="G11" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="18" t="n">
-        <v>3911</v>
-      </c>
-      <c r="I11" s="18" t="n">
-        <v>3277444</v>
+      <c r="F11" s="21" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>4511</v>
+      </c>
+      <c r="I11" s="21" t="n">
+        <v>3605644</v>
       </c>
     </row>
   </sheetData>
@@ -2015,121 +2056,121 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>MASIL — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>В пути</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Приход 12.10</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>Бишкек</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>Итого РФ</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>8809744060125</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>183030830</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>MASIL - 8 Seconds Salon Hair Mask 350ml Set [350ml+8ml*2]</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="18" t="n">
         <v>729</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="18" t="n">
         <v>103</v>
       </c>
-      <c r="F4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n">
+      <c r="F4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="n">
         <v>103</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="18" t="n">
         <v>75087</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="A5" s="19" t="n"/>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="18" t="n">
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="21" t="n">
         <v>103</v>
       </c>
-      <c r="F5" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="18" t="n">
+      <c r="F5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="21" t="n">
         <v>103</v>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="I5" s="21" t="n">
         <v>75087</v>
       </c>
     </row>
@@ -2152,691 +2193,691 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>PETITFEE — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>В пути</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Приход 12.10</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>Бишкек</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>Итого РФ</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>8809508850443</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>226115324</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs] / Охлаждающая гидрогелевая маска для лица с экстрактом агавы</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="18" t="n">
         <v>546</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="18" t="n">
         <v>498</v>
       </c>
-      <c r="F4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n">
+      <c r="F4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="n">
         <v>498</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="18" t="n">
         <v>271908</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>8809239800458</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>179611231</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>PETITFEE - Collagen &amp; CoQ10 Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с коллагеном и коэнзимом Q10</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="18" t="n">
         <v>445</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="18" t="n">
         <v>504</v>
       </c>
-      <c r="F5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="15" t="n">
+      <c r="F5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="n">
         <v>504</v>
       </c>
-      <c r="I5" s="15" t="n">
+      <c r="I5" s="18" t="n">
         <v>224280</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>8809508850504</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>180988755</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="18" t="n">
         <v>547</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="18" t="n">
         <v>380</v>
       </c>
-      <c r="F6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="15" t="n">
+      <c r="F6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="18" t="n">
         <v>380</v>
       </c>
-      <c r="I6" s="15" t="n">
+      <c r="I6" s="18" t="n">
         <v>207860</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>4626999886126</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>226114935</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="18" t="n">
         <v>567</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="18" t="n">
         <v>330</v>
       </c>
-      <c r="F7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="15" t="n"/>
-      <c r="H7" s="15" t="n">
+      <c r="F7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="18" t="n">
         <v>330</v>
       </c>
-      <c r="I7" s="15" t="n">
+      <c r="I7" s="18" t="n">
         <v>187110</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>8809508850672</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>226115248</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs] / Тонизирующая гидрогелевая маска для лица с экстрактом какао</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="18" t="n">
         <v>557</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="18" t="n">
         <v>258</v>
       </c>
-      <c r="F8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="15" t="n"/>
-      <c r="H8" s="15" t="n">
+      <c r="F8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="18" t="n">
         <v>258</v>
       </c>
-      <c r="I8" s="15" t="n">
+      <c r="I8" s="18" t="n">
         <v>143706</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>8809508850511</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>226114831</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs] / Смягчающая гидрогелевая маска для лица с экстрактом артишока</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="18" t="n">
         <v>559</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="18" t="n">
         <v>248</v>
       </c>
-      <c r="F9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="15" t="n"/>
-      <c r="H9" s="15" t="n">
+      <c r="F9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="n">
         <v>248</v>
       </c>
-      <c r="I9" s="15" t="n">
+      <c r="I9" s="18" t="n">
         <v>138632</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>4626999886010</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>226115141</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом и экстрактом улитки</t>
         </is>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="18" t="n">
         <v>538</v>
       </c>
-      <c r="E10" s="15" t="n">
+      <c r="E10" s="18" t="n">
         <v>239</v>
       </c>
-      <c r="F10" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="15" t="n"/>
-      <c r="H10" s="15" t="n">
+      <c r="F10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="18" t="n"/>
+      <c r="H10" s="18" t="n">
         <v>239</v>
       </c>
-      <c r="I10" s="15" t="n">
+      <c r="I10" s="18" t="n">
         <v>128582</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>8809239803596</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>180711104</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>PETITFEE - Gold Hydrogel Eye Patch [60ea] / гидрогелевые патчи для глаз с золотом</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="18" t="n">
         <v>475</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="18" t="n">
         <v>261</v>
       </c>
-      <c r="F11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="15" t="n"/>
-      <c r="H11" s="15" t="n">
+      <c r="F11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="18" t="n"/>
+      <c r="H11" s="18" t="n">
         <v>261</v>
       </c>
-      <c r="I11" s="15" t="n">
+      <c r="I11" s="18" t="n">
         <v>123975</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>8809508850498</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>180987509</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>PETITFEE - Pink Vita Brightening Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
         </is>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="18" t="n">
         <v>547</v>
       </c>
-      <c r="E12" s="15" t="n">
+      <c r="E12" s="18" t="n">
         <v>190</v>
       </c>
-      <c r="F12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="15" t="n"/>
-      <c r="H12" s="15" t="n">
+      <c r="F12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="n">
         <v>190</v>
       </c>
-      <c r="I12" s="15" t="n">
+      <c r="I12" s="18" t="n">
         <v>103930</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>4626999886003</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>226115478</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с черным жемчугом и золотом</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="18" t="n">
         <v>538</v>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E13" s="18" t="n">
         <v>167</v>
       </c>
-      <c r="F13" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="15" t="n"/>
-      <c r="H13" s="15" t="n">
+      <c r="F13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="18" t="n"/>
+      <c r="H13" s="18" t="n">
         <v>167</v>
       </c>
-      <c r="I13" s="15" t="n">
+      <c r="I13" s="18" t="n">
         <v>89846</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>8809239802872</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>179611207</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>PETITFEE - Gold &amp; Snail Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с золотом и улиткой</t>
         </is>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="18" t="n">
         <v>475</v>
       </c>
-      <c r="E14" s="15" t="n">
+      <c r="E14" s="18" t="n">
         <v>186</v>
       </c>
-      <c r="F14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="15" t="n"/>
-      <c r="H14" s="15" t="n">
+      <c r="F14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="18" t="n">
         <v>186</v>
       </c>
-      <c r="I14" s="15" t="n">
+      <c r="I14" s="18" t="n">
         <v>88350</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>8809239801820</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>151175880</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с черным жемчугом и золотом</t>
         </is>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D15" s="18" t="n">
         <v>448</v>
       </c>
-      <c r="E15" s="15" t="n">
+      <c r="E15" s="18" t="n">
         <v>169</v>
       </c>
-      <c r="F15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="15" t="n"/>
-      <c r="H15" s="15" t="n">
+      <c r="F15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="18" t="n">
         <v>169</v>
       </c>
-      <c r="I15" s="15" t="n">
+      <c r="I15" s="18" t="n">
         <v>75712</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>8809508850696</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>179611304</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea] / Тонизирующие гидрогелевые патчи для глаз с экстрактом какао</t>
         </is>
       </c>
-      <c r="D16" s="15" t="n">
+      <c r="D16" s="18" t="n">
         <v>475</v>
       </c>
-      <c r="E16" s="15" t="n">
+      <c r="E16" s="18" t="n">
         <v>141</v>
       </c>
-      <c r="F16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="15" t="n"/>
-      <c r="H16" s="15" t="n">
+      <c r="F16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="18" t="n">
         <v>141</v>
       </c>
-      <c r="I16" s="15" t="n">
+      <c r="I16" s="18" t="n">
         <v>66975</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>8809508850429</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>151175877</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea] / Охлаждающие гидрогелевые патчи для глаз с экстрактом агавы</t>
         </is>
       </c>
-      <c r="D17" s="15" t="n">
+      <c r="D17" s="18" t="n">
         <v>475</v>
       </c>
-      <c r="E17" s="15" t="n">
+      <c r="E17" s="18" t="n">
         <v>131</v>
       </c>
-      <c r="F17" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="15" t="n"/>
-      <c r="H17" s="15" t="n">
+      <c r="F17" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="18" t="n"/>
+      <c r="H17" s="18" t="n">
         <v>131</v>
       </c>
-      <c r="I17" s="15" t="n">
+      <c r="I17" s="18" t="n">
         <v>62225</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr"/>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr"/>
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>1175175447</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>PETITFEE - MASK 6 (блек, агава, какао, артишок, голд, ромашка)</t>
         </is>
       </c>
-      <c r="D18" s="15" t="n">
+      <c r="D18" s="18" t="n">
         <v>653</v>
       </c>
-      <c r="E18" s="15" t="n">
+      <c r="E18" s="18" t="n">
         <v>86</v>
       </c>
-      <c r="F18" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="15" t="n"/>
-      <c r="H18" s="15" t="n">
+      <c r="F18" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="18" t="n"/>
+      <c r="H18" s="18" t="n">
         <v>86</v>
       </c>
-      <c r="I18" s="15" t="n">
+      <c r="I18" s="18" t="n">
         <v>56158</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr"/>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr"/>
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>1177994944</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>PETITFEE - MASK 5 (блек, агава, какао, артишок, голд снейл)</t>
         </is>
       </c>
-      <c r="D19" s="15" t="n">
+      <c r="D19" s="18" t="n">
         <v>548</v>
       </c>
-      <c r="E19" s="15" t="n">
+      <c r="E19" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="F19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="15" t="n"/>
-      <c r="H19" s="15" t="n">
+      <c r="F19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="18" t="n"/>
+      <c r="H19" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="I19" s="15" t="n">
+      <c r="I19" s="18" t="n">
         <v>54800</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>8809508850801</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>180992464</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
         </is>
       </c>
-      <c r="D20" s="15" t="n">
+      <c r="D20" s="18" t="n">
         <v>651</v>
       </c>
-      <c r="E20" s="15" t="n">
+      <c r="E20" s="18" t="n">
         <v>60</v>
       </c>
-      <c r="F20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="15" t="n"/>
-      <c r="H20" s="15" t="n">
+      <c r="F20" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="18" t="n"/>
+      <c r="H20" s="18" t="n">
         <v>60</v>
       </c>
-      <c r="I20" s="15" t="n">
+      <c r="I20" s="18" t="n">
         <v>39060</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>8809508850503</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr"/>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr"/>
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [1 pairs]/ Гидрогелевые патчи для глаз с черным жемчугом и золотом 1 пара</t>
         </is>
       </c>
-      <c r="D21" s="20" t="n"/>
-      <c r="E21" s="20" t="n">
+      <c r="D21" s="23" t="n"/>
+      <c r="E21" s="23" t="n">
         <v>320</v>
       </c>
-      <c r="F21" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="15" t="n"/>
-      <c r="H21" s="20" t="n">
+      <c r="F21" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="18" t="n"/>
+      <c r="H21" s="23" t="n">
         <v>320</v>
       </c>
-      <c r="I21" s="20" t="n"/>
+      <c r="I21" s="23" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>8809508850597</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr"/>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr"/>
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>PETITFEE - Gold Hydrogel Eye Patch [1 Pairs] / гидрогелевые патчи для глаз с золотом 1 пара</t>
         </is>
       </c>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="20" t="n">
+      <c r="D22" s="23" t="n"/>
+      <c r="E22" s="23" t="n">
         <v>428</v>
       </c>
-      <c r="F22" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="15" t="n"/>
-      <c r="H22" s="20" t="n">
+      <c r="F22" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="18" t="n"/>
+      <c r="H22" s="23" t="n">
         <v>428</v>
       </c>
-      <c r="I22" s="20" t="n"/>
+      <c r="I22" s="23" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="n"/>
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="A23" s="19" t="n"/>
+      <c r="B23" s="19" t="n"/>
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D23" s="16" t="n"/>
-      <c r="E23" s="18" t="n">
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="21" t="n">
         <v>4696</v>
       </c>
-      <c r="F23" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="18" t="n">
+      <c r="F23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="21" t="n">
         <v>4696</v>
       </c>
-      <c r="I23" s="18" t="n">
+      <c r="I23" s="21" t="n">
         <v>2063109</v>
       </c>
     </row>
@@ -2859,450 +2900,450 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>ROUND LAB — площадка: OZON</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="22" t="inlineStr">
+      <c r="D3" s="25" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="25" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="22" t="inlineStr">
-        <is>
-          <t>В пути</t>
-        </is>
-      </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="F3" s="25" t="inlineStr">
+        <is>
+          <t>Приход 12.10</t>
+        </is>
+      </c>
+      <c r="G3" s="25" t="inlineStr">
         <is>
           <t>Бишкек</t>
         </is>
       </c>
-      <c r="H3" s="22" t="inlineStr">
+      <c r="H3" s="25" t="inlineStr">
         <is>
           <t>Итого РФ</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="25" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>8809738608364</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>437154709</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="18" t="n">
         <v>572</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="18" t="n">
         <v>2799</v>
       </c>
-      <c r="F4" s="15" t="n">
+      <c r="F4" s="18" t="n">
         <v>10020</v>
       </c>
-      <c r="G4" s="23" t="n">
+      <c r="G4" s="26" t="n">
         <v>15000</v>
       </c>
-      <c r="H4" s="15" t="n">
+      <c r="H4" s="18" t="n">
         <v>12819</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="18" t="n">
         <v>7332468</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>8809738593080</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>437242640</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка для умывания лица от прыщей и акне</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="18" t="n">
         <v>572</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="18" t="n">
         <v>1188</v>
       </c>
-      <c r="F5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="15" t="n">
+      <c r="F5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="n">
         <v>1188</v>
       </c>
-      <c r="I5" s="15" t="n">
+      <c r="I5" s="18" t="n">
         <v>679536</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>8809657114731</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr"/>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr"/>
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="18" t="n">
         <v>684</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="18" t="n">
         <v>559</v>
       </c>
-      <c r="F6" s="15" t="n">
+      <c r="F6" s="18" t="n">
         <v>360</v>
       </c>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="15" t="n">
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="18" t="n">
         <v>919</v>
       </c>
-      <c r="I6" s="15" t="n">
+      <c r="I6" s="18" t="n">
         <v>628596</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>8809962541840</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr"/>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr"/>
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>ROUND LAB CAMELLIA DEEP COLLAGEN FIRMING CREAM_50ml</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="18" t="n">
         <v>1056</v>
       </c>
-      <c r="E7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="15" t="n">
+      <c r="E7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="18" t="n">
         <v>400</v>
       </c>
-      <c r="G7" s="15" t="n"/>
-      <c r="H7" s="15" t="n">
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="18" t="n">
         <v>400</v>
       </c>
-      <c r="I7" s="15" t="n">
+      <c r="I7" s="18" t="n">
         <v>422400</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>8809738599044</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr"/>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr"/>
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>1025 DOKDO BUBBLE FOAM_150ml</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="18" t="n">
         <v>655</v>
       </c>
-      <c r="E8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="15" t="n">
+      <c r="E8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="18" t="n">
         <v>600</v>
       </c>
-      <c r="G8" s="15" t="n"/>
-      <c r="H8" s="15" t="n">
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="18" t="n">
         <v>600</v>
       </c>
-      <c r="I8" s="15" t="n">
+      <c r="I8" s="18" t="n">
         <v>393000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>8809864754126</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr"/>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr"/>
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>PINE CALMING CICA CLEANSER_150ml</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="18" t="n">
         <v>591</v>
       </c>
-      <c r="E9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="15" t="n">
+      <c r="E9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="18" t="n">
         <v>600</v>
       </c>
-      <c r="G9" s="15" t="n"/>
-      <c r="H9" s="15" t="n">
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="n">
         <v>600</v>
       </c>
-      <c r="I9" s="15" t="n">
+      <c r="I9" s="18" t="n">
         <v>354600</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>8809849802408</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr"/>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr"/>
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>PINE CALMING CICA BODY WASH_400ml</t>
         </is>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="18" t="n">
         <v>691</v>
       </c>
-      <c r="E10" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="15" t="n">
+      <c r="E10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="18" t="n">
         <v>400</v>
       </c>
-      <c r="G10" s="15" t="n"/>
-      <c r="H10" s="15" t="n">
+      <c r="G10" s="18" t="n"/>
+      <c r="H10" s="18" t="n">
         <v>400</v>
       </c>
-      <c r="I10" s="15" t="n">
+      <c r="I10" s="18" t="n">
         <v>276400</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>8809750462708</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr"/>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr"/>
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>PINE CALMING CICA PAD_50pcs</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="18" t="n">
         <v>892</v>
       </c>
-      <c r="E11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="15" t="n">
+      <c r="E11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="18" t="n">
         <v>270</v>
       </c>
-      <c r="G11" s="15" t="n"/>
-      <c r="H11" s="15" t="n">
+      <c r="G11" s="18" t="n"/>
+      <c r="H11" s="18" t="n">
         <v>270</v>
       </c>
-      <c r="I11" s="15" t="n">
+      <c r="I11" s="18" t="n">
         <v>240840</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>8809962542137</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr"/>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr"/>
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>PINE CALMING CICA CREAM PLUS_60ml</t>
         </is>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="18" t="n">
         <v>992</v>
       </c>
-      <c r="E12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="15" t="n">
+      <c r="E12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="18" t="n">
         <v>240</v>
       </c>
-      <c r="G12" s="15" t="n"/>
-      <c r="H12" s="15" t="n">
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="n">
         <v>240</v>
       </c>
-      <c r="I12" s="15" t="n">
+      <c r="I12" s="18" t="n">
         <v>238080</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>8809738593240</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr"/>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr"/>
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>SOYBEAN SERUM_50ml</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="18" t="n">
         <v>934</v>
       </c>
-      <c r="E13" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="15" t="n">
+      <c r="E13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="18" t="n">
         <v>210</v>
       </c>
-      <c r="G13" s="15" t="n"/>
-      <c r="H13" s="15" t="n">
+      <c r="G13" s="18" t="n"/>
+      <c r="H13" s="18" t="n">
         <v>210</v>
       </c>
-      <c r="I13" s="15" t="n">
+      <c r="I13" s="18" t="n">
         <v>196140</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>8809962540553</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr"/>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr"/>
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>ROUND LAB STICK POUCH KIT</t>
         </is>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="18" t="n">
         <v>555</v>
       </c>
-      <c r="E14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="15" t="n">
+      <c r="E14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="G14" s="15" t="n"/>
-      <c r="H14" s="15" t="n">
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I14" s="15" t="n">
+      <c r="I14" s="18" t="n">
         <v>166500</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>8809738600221</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>437190353</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем  с березовым соком</t>
         </is>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D15" s="18" t="n">
         <v>1153</v>
       </c>
-      <c r="E15" s="15" t="n">
+      <c r="E15" s="18" t="n">
         <v>33</v>
       </c>
-      <c r="F15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="15" t="n"/>
-      <c r="H15" s="15" t="n">
+      <c r="F15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="18" t="n">
         <v>33</v>
       </c>
-      <c r="I15" s="15" t="n">
+      <c r="I15" s="18" t="n">
         <v>38049</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n"/>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="A16" s="19" t="n"/>
+      <c r="B16" s="19" t="n"/>
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D16" s="16" t="n"/>
-      <c r="E16" s="18" t="n">
+      <c r="D16" s="19" t="n"/>
+      <c r="E16" s="21" t="n">
         <v>4579</v>
       </c>
-      <c r="F16" s="18" t="n">
+      <c r="F16" s="21" t="n">
         <v>13400</v>
       </c>
-      <c r="G16" s="18" t="n">
+      <c r="G16" s="21" t="n">
         <v>15000</v>
       </c>
-      <c r="H16" s="18" t="n">
+      <c r="H16" s="21" t="n">
         <v>17979</v>
       </c>
-      <c r="I16" s="18" t="n">
+      <c r="I16" s="21" t="n">
         <v>10966609</v>
       </c>
     </row>
@@ -3325,241 +3366,241 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>SKIN1004 — площадка: OZON</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="22" t="inlineStr">
+      <c r="D3" s="25" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="25" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="22" t="inlineStr">
-        <is>
-          <t>В пути</t>
-        </is>
-      </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="F3" s="25" t="inlineStr">
+        <is>
+          <t>Приход 12.10</t>
+        </is>
+      </c>
+      <c r="G3" s="25" t="inlineStr">
         <is>
           <t>Бишкек</t>
         </is>
       </c>
-      <c r="H3" s="22" t="inlineStr">
+      <c r="H3" s="25" t="inlineStr">
         <is>
           <t>Итого РФ</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="25" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>8809576260601</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr"/>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr"/>
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>SKIN1004 Madagascar Centella Ampoule 55ml</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="18" t="n">
         <v>734</v>
       </c>
-      <c r="E4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="15" t="n">
+      <c r="E4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="18" t="n">
         <v>1500</v>
       </c>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n">
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="n">
         <v>1500</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="18" t="n">
         <v>1101000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>8809576261134</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr"/>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr"/>
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>SKIN1004 Madagascar Centella Soothing Cream 75ml</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="18" t="n">
         <v>917</v>
       </c>
-      <c r="E5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="15" t="n">
+      <c r="E5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="18" t="n">
         <v>920</v>
       </c>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="15" t="n">
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="n">
         <v>920</v>
       </c>
-      <c r="I5" s="15" t="n">
+      <c r="I5" s="18" t="n">
         <v>843640</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>8809576261172</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr"/>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr"/>
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>SKIN1004 Madagascar Centella Tone Brightening Capsule Ampoule 100ml</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="18" t="n">
         <v>925</v>
       </c>
-      <c r="E6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="15" t="n">
+      <c r="E6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="18" t="n">
         <v>900</v>
       </c>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="15" t="n">
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="18" t="n">
         <v>900</v>
       </c>
-      <c r="I6" s="15" t="n">
+      <c r="I6" s="18" t="n">
         <v>832500</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>8809576260618</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>214311963</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="18" t="n">
         <v>428</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="18" t="n">
         <v>28</v>
       </c>
-      <c r="F7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="15" t="n"/>
-      <c r="H7" s="15" t="n">
+      <c r="F7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="18" t="n">
         <v>28</v>
       </c>
-      <c r="I7" s="15" t="n">
+      <c r="I7" s="18" t="n">
         <v>11984</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>8809576260724</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>214312149</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>SKIN1004 - Madagascar Centella Hyalu-Cica Sleeping Pack [30ml] / Увлажняющая гиалуроновая ночная маска для сухой кожи</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="18" t="n">
         <v>354</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="18" t="n">
         <v>21</v>
       </c>
-      <c r="F8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="15" t="n"/>
-      <c r="H8" s="15" t="n">
+      <c r="F8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="18" t="n">
         <v>21</v>
       </c>
-      <c r="I8" s="15" t="n">
+      <c r="I8" s="18" t="n">
         <v>7434</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n"/>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="A9" s="19" t="n"/>
+      <c r="B9" s="19" t="n"/>
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="18" t="n">
+      <c r="D9" s="19" t="n"/>
+      <c r="E9" s="21" t="n">
         <v>49</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="21" t="n">
         <v>3320</v>
       </c>
-      <c r="G9" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="18" t="n">
+      <c r="G9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="21" t="n">
         <v>3369</v>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="21" t="n">
         <v>2796558</v>
       </c>
     </row>
@@ -3582,150 +3623,150 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>SOME BY MI — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>В пути</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Приход 12.10</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>Бишкек</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>Итого РФ</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>8809408260793</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>248928046</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cleansing Bar [106g] / Мыло для проблемной кожи с aha bha кислотами</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="18" t="n">
         <v>610</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="18" t="n">
         <v>525</v>
       </c>
-      <c r="F4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n">
+      <c r="F4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="n">
         <v>525</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="18" t="n">
         <v>320250</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr"/>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr"/>
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>248929125</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] /  Крем для лица</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="18" t="n">
         <v>1117</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="18" t="n">
         <v>55</v>
       </c>
-      <c r="F5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="15" t="n">
+      <c r="F5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="n">
         <v>55</v>
       </c>
-      <c r="I5" s="15" t="n">
+      <c r="I5" s="18" t="n">
         <v>61435</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n"/>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="A6" s="19" t="n"/>
+      <c r="B6" s="19" t="n"/>
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="18" t="n">
+      <c r="D6" s="19" t="n"/>
+      <c r="E6" s="21" t="n">
         <v>580</v>
       </c>
-      <c r="F6" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="18" t="n">
+      <c r="F6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="21" t="n">
         <v>580</v>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="21" t="n">
         <v>381685</v>
       </c>
     </row>
@@ -3748,154 +3789,154 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>THE ORDINARY — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>В пути</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Приход 12.10</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>Бишкек</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>Итого РФ</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>769915190946</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>214312385</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>THE ORDINARY - Argireline Solution 10% [30ml] / Сыворотка для лица от прыщей и акне с ниацинамидом 10 %</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="18" t="n">
         <v>782</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="18" t="n">
         <v>95</v>
       </c>
-      <c r="F4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n">
+      <c r="F4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="n">
         <v>95</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="18" t="n">
         <v>74290</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>769915196498</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>247275092</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="18" t="n">
         <v>905</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="F5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="15" t="n">
+      <c r="F5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="I5" s="15" t="n">
+      <c r="I5" s="18" t="n">
         <v>22625</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n"/>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="A6" s="19" t="n"/>
+      <c r="B6" s="19" t="n"/>
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="18" t="n">
+      <c r="D6" s="19" t="n"/>
+      <c r="E6" s="21" t="n">
         <v>120</v>
       </c>
-      <c r="F6" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="18" t="n">
+      <c r="F6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="21" t="n">
         <v>120</v>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="21" t="n">
         <v>96915</v>
       </c>
     </row>
@@ -3918,121 +3959,121 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>COSRX — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>В пути</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Приход 12.10</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>Бишкек</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>Итого РФ</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>8809416471112</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>204258828</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>COSRX - Salicylic Acid Daily Gentle Cleanser [150ml] / Пенка с салициловой кислотой для проблемной кожи</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="18" t="n">
         <v>404</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="18" t="n">
         <v>185</v>
       </c>
-      <c r="F4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n">
+      <c r="F4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="n">
         <v>185</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="18" t="n">
         <v>74740</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="A5" s="19" t="n"/>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="18" t="n">
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="21" t="n">
         <v>185</v>
       </c>
-      <c r="F5" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="18" t="n">
+      <c r="F5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="21" t="n">
         <v>185</v>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="I5" s="21" t="n">
         <v>74740</v>
       </c>
     </row>
@@ -4055,913 +4096,913 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>CELIMAX — площадка: OZON</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="22" t="inlineStr">
+      <c r="D3" s="25" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="25" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="22" t="inlineStr">
-        <is>
-          <t>В пути</t>
-        </is>
-      </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="F3" s="25" t="inlineStr">
+        <is>
+          <t>Приход 12.10</t>
+        </is>
+      </c>
+      <c r="G3" s="25" t="inlineStr">
         <is>
           <t>Бишкек</t>
         </is>
       </c>
-      <c r="H3" s="22" t="inlineStr">
+      <c r="H3" s="25" t="inlineStr">
         <is>
           <t>Итого РФ</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="25" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>8809606850475</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>868516027</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Celimax Dual Barrier Creamy Toner, тонер 150 мл</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="18" t="n">
         <v>888</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="18" t="n">
         <v>13908</v>
       </c>
-      <c r="F4" s="15" t="n">
+      <c r="F4" s="18" t="n">
         <v>10008</v>
       </c>
-      <c r="G4" s="23" t="n">
+      <c r="G4" s="26" t="n">
         <v>15000</v>
       </c>
-      <c r="H4" s="15" t="n">
+      <c r="H4" s="18" t="n">
         <v>23916</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="18" t="n">
         <v>21237408</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>8809700320812</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>551387355</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]/Подтягивающий бустер-крем с ретинолом для лица</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="18" t="n">
         <v>572</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="18" t="n">
         <v>5658</v>
       </c>
-      <c r="F5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="15" t="n">
+      <c r="F5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="n">
         <v>5658</v>
       </c>
-      <c r="I5" s="15" t="n">
+      <c r="I5" s="18" t="n">
         <v>3236376</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>8809783321225</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>551607905</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="18" t="n">
         <v>768</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="18" t="n">
         <v>1432</v>
       </c>
-      <c r="F6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="15" t="n">
+      <c r="F6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="18" t="n">
         <v>1432</v>
       </c>
-      <c r="I6" s="15" t="n">
+      <c r="I6" s="18" t="n">
         <v>1099776</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>8809782557861</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr"/>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr"/>
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL CICA SOOTHING CREAM 50ML</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="18" t="n">
         <v>732</v>
       </c>
-      <c r="E7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="15" t="n">
+      <c r="E7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="18" t="n">
         <v>1200</v>
       </c>
-      <c r="G7" s="15" t="n"/>
-      <c r="H7" s="15" t="n">
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="18" t="n">
         <v>1200</v>
       </c>
-      <c r="I7" s="15" t="n">
+      <c r="I7" s="18" t="n">
         <v>878400</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>8809743546323</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>551540924</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="18" t="n">
         <v>616</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="18" t="n">
         <v>1362</v>
       </c>
-      <c r="F8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="15" t="n"/>
-      <c r="H8" s="15" t="n">
+      <c r="F8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="18" t="n">
         <v>1362</v>
       </c>
-      <c r="I8" s="15" t="n">
+      <c r="I8" s="18" t="n">
         <v>838992</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>8809463992615</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr"/>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr"/>
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>CELIMAX JI WOO GAE HEARTLEAF BHA PEELING PAD 60PADS</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="18" t="n">
         <v>672</v>
       </c>
-      <c r="E9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="15" t="n">
+      <c r="E9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="18" t="n">
         <v>1200</v>
       </c>
-      <c r="G9" s="15" t="n"/>
-      <c r="H9" s="15" t="n">
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="n">
         <v>1200</v>
       </c>
-      <c r="I9" s="15" t="n">
+      <c r="I9" s="18" t="n">
         <v>806400</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>8809743544626</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr"/>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr"/>
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL CICA NIACINAMIDE AC CALMING SERUM 40ML</t>
         </is>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="18" t="n">
         <v>886</v>
       </c>
-      <c r="E10" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="15" t="n">
+      <c r="E10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="18" t="n">
         <v>864</v>
       </c>
-      <c r="G10" s="15" t="n"/>
-      <c r="H10" s="15" t="n">
+      <c r="G10" s="18" t="n"/>
+      <c r="H10" s="18" t="n">
         <v>864</v>
       </c>
-      <c r="I10" s="15" t="n">
+      <c r="I10" s="18" t="n">
         <v>765504</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>8809750465464</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr"/>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr"/>
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL NONI CALMING GLOW PAD 50EA</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="18" t="n">
         <v>771</v>
       </c>
-      <c r="E11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="15" t="n">
+      <c r="E11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="18" t="n">
         <v>984</v>
       </c>
-      <c r="G11" s="15" t="n"/>
-      <c r="H11" s="15" t="n">
+      <c r="G11" s="18" t="n"/>
+      <c r="H11" s="18" t="n">
         <v>984</v>
       </c>
-      <c r="I11" s="15" t="n">
+      <c r="I11" s="18" t="n">
         <v>758664</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>8809700320805</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>551465879</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинолом и микроиглами для лица</t>
         </is>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="18" t="n">
         <v>592</v>
       </c>
-      <c r="E12" s="15" t="n">
+      <c r="E12" s="18" t="n">
         <v>1255</v>
       </c>
-      <c r="F12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="15" t="n"/>
-      <c r="H12" s="15" t="n">
+      <c r="F12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="n">
         <v>1255</v>
       </c>
-      <c r="I12" s="15" t="n">
+      <c r="I12" s="18" t="n">
         <v>742960</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>8809686386185</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr"/>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr"/>
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL NONI ENERGY REPAIR CREAM 50ML</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="18" t="n">
         <v>1020</v>
       </c>
-      <c r="E13" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="15" t="n">
+      <c r="E13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="18" t="n">
         <v>720</v>
       </c>
-      <c r="G13" s="15" t="n"/>
-      <c r="H13" s="15" t="n">
+      <c r="G13" s="18" t="n"/>
+      <c r="H13" s="18" t="n">
         <v>720</v>
       </c>
-      <c r="I13" s="15" t="n">
+      <c r="I13" s="18" t="n">
         <v>734400</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>8809743546880</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr"/>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr"/>
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>CELIMAX OIL CONTROL MOISTURIZING CREAM 80ML</t>
         </is>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="18" t="n">
         <v>848</v>
       </c>
-      <c r="E14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="15" t="n">
+      <c r="E14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="18" t="n">
         <v>600</v>
       </c>
-      <c r="G14" s="15" t="n"/>
-      <c r="H14" s="15" t="n">
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="18" t="n">
         <v>600</v>
       </c>
-      <c r="I14" s="15" t="n">
+      <c r="I14" s="18" t="n">
         <v>508800</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>8800296551789</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr"/>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr"/>
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>CELIMAX PORE+DARK SPOT BRIGHTENING KIT</t>
         </is>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D15" s="18" t="n">
         <v>590</v>
       </c>
-      <c r="E15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="15" t="n">
+      <c r="E15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="18" t="n">
         <v>576</v>
       </c>
-      <c r="G15" s="15" t="n"/>
-      <c r="H15" s="15" t="n">
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="18" t="n">
         <v>576</v>
       </c>
-      <c r="I15" s="15" t="n">
+      <c r="I15" s="18" t="n">
         <v>339840</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>8809971482349</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr"/>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr"/>
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL NONI STARTER KIT</t>
         </is>
       </c>
-      <c r="D16" s="15" t="n">
+      <c r="D16" s="18" t="n">
         <v>692</v>
       </c>
-      <c r="E16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="15" t="n">
+      <c r="E16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="18" t="n">
         <v>480</v>
       </c>
-      <c r="G16" s="15" t="n"/>
-      <c r="H16" s="15" t="n">
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="18" t="n">
         <v>480</v>
       </c>
-      <c r="I16" s="15" t="n">
+      <c r="I16" s="18" t="n">
         <v>332160</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>8809463992707</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr"/>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr"/>
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>CELIMAX ONE STEP BODY BRIGHTENING PAD 60PADS</t>
         </is>
       </c>
-      <c r="D17" s="15" t="n">
+      <c r="D17" s="18" t="n">
         <v>567</v>
       </c>
-      <c r="E17" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="15" t="n">
+      <c r="E17" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="18" t="n">
         <v>528</v>
       </c>
-      <c r="G17" s="15" t="n"/>
-      <c r="H17" s="15" t="n">
+      <c r="G17" s="18" t="n"/>
+      <c r="H17" s="18" t="n">
         <v>528</v>
       </c>
-      <c r="I17" s="15" t="n">
+      <c r="I17" s="18" t="n">
         <v>299376</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>8809626564000</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr"/>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr"/>
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>CELIMAX DERMA NATURE GLUTATHIONE LONGLASTING TONE-UP CREAM 35ML</t>
         </is>
       </c>
-      <c r="D18" s="15" t="n">
+      <c r="D18" s="18" t="n">
         <v>592</v>
       </c>
-      <c r="E18" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="15" t="n">
+      <c r="E18" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="18" t="n">
         <v>468</v>
       </c>
-      <c r="G18" s="15" t="n"/>
-      <c r="H18" s="15" t="n">
+      <c r="G18" s="18" t="n"/>
+      <c r="H18" s="18" t="n">
         <v>468</v>
       </c>
-      <c r="I18" s="15" t="n">
+      <c r="I18" s="18" t="n">
         <v>277056</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>8809954940354</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr"/>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr"/>
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL NONI REFRESH CLAY MASK 120G</t>
         </is>
       </c>
-      <c r="D19" s="15" t="n">
+      <c r="D19" s="18" t="n">
         <v>610</v>
       </c>
-      <c r="E19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="15" t="n">
+      <c r="E19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="18" t="n">
         <v>408</v>
       </c>
-      <c r="G19" s="15" t="n"/>
-      <c r="H19" s="15" t="n">
+      <c r="G19" s="18" t="n"/>
+      <c r="H19" s="18" t="n">
         <v>408</v>
       </c>
-      <c r="I19" s="15" t="n">
+      <c r="I19" s="18" t="n">
         <v>248880</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>8809606852332</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr"/>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr"/>
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>CELIMAX DUAL BARRIER TRIAL KIT</t>
         </is>
       </c>
-      <c r="D20" s="15" t="n">
+      <c r="D20" s="18" t="n">
         <v>509</v>
       </c>
-      <c r="E20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="15" t="n">
+      <c r="E20" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="18" t="n">
         <v>448</v>
       </c>
-      <c r="G20" s="15" t="n"/>
-      <c r="H20" s="15" t="n">
+      <c r="G20" s="18" t="n"/>
+      <c r="H20" s="18" t="n">
         <v>448</v>
       </c>
-      <c r="I20" s="15" t="n">
+      <c r="I20" s="18" t="n">
         <v>228032</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>8809463993889</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr"/>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr"/>
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>CELIMAX JI WOO GAE ONE STEP MILD CLEANSING PAD 60PADS</t>
         </is>
       </c>
-      <c r="D21" s="15" t="n">
+      <c r="D21" s="18" t="n">
         <v>631</v>
       </c>
-      <c r="E21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="15" t="n">
+      <c r="E21" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="18" t="n">
         <v>352</v>
       </c>
-      <c r="G21" s="15" t="n"/>
-      <c r="H21" s="15" t="n">
+      <c r="G21" s="18" t="n"/>
+      <c r="H21" s="18" t="n">
         <v>352</v>
       </c>
-      <c r="I21" s="15" t="n">
+      <c r="I21" s="18" t="n">
         <v>222112</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>8809606850499</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr"/>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr"/>
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>CELIMAX DUAL BARRIER MILD GEL CLEANSER 200ML</t>
         </is>
       </c>
-      <c r="D22" s="15" t="n">
+      <c r="D22" s="18" t="n">
         <v>727</v>
       </c>
-      <c r="E22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="15" t="n">
+      <c r="E22" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="18" t="n">
         <v>288</v>
       </c>
-      <c r="G22" s="15" t="n"/>
-      <c r="H22" s="15" t="n">
+      <c r="G22" s="18" t="n"/>
+      <c r="H22" s="18" t="n">
         <v>288</v>
       </c>
-      <c r="I22" s="15" t="n">
+      <c r="I22" s="18" t="n">
         <v>209376</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>8806050298525</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr"/>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr"/>
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>CELIMAX DERMA NATURE FRESH BLACKHEAD JOJOBA CLEANSING OIL 150ML</t>
         </is>
       </c>
-      <c r="D23" s="15" t="n">
+      <c r="D23" s="18" t="n">
         <v>651</v>
       </c>
-      <c r="E23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="15" t="n">
+      <c r="E23" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="18" t="n">
         <v>315</v>
       </c>
-      <c r="G23" s="15" t="n"/>
-      <c r="H23" s="15" t="n">
+      <c r="G23" s="18" t="n"/>
+      <c r="H23" s="18" t="n">
         <v>315</v>
       </c>
-      <c r="I23" s="15" t="n">
+      <c r="I23" s="18" t="n">
         <v>205065</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>8809783323519</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>551600265</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
         </is>
       </c>
-      <c r="D24" s="15" t="n">
+      <c r="D24" s="18" t="n">
         <v>157</v>
       </c>
-      <c r="E24" s="15" t="n">
+      <c r="E24" s="18" t="n">
         <v>1252</v>
       </c>
-      <c r="F24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="15" t="n"/>
-      <c r="H24" s="15" t="n">
+      <c r="F24" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="18" t="n"/>
+      <c r="H24" s="18" t="n">
         <v>1252</v>
       </c>
-      <c r="I24" s="15" t="n">
+      <c r="I24" s="18" t="n">
         <v>196564</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>8809541379468</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr"/>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr"/>
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL NONI ACNE BUBBLE CLEANSER 155ML</t>
         </is>
       </c>
-      <c r="D25" s="15" t="n">
+      <c r="D25" s="18" t="n">
         <v>605</v>
       </c>
-      <c r="E25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="15" t="n">
+      <c r="E25" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="18" t="n">
         <v>312</v>
       </c>
-      <c r="G25" s="15" t="n"/>
-      <c r="H25" s="15" t="n">
+      <c r="G25" s="18" t="n"/>
+      <c r="H25" s="18" t="n">
         <v>312</v>
       </c>
-      <c r="I25" s="15" t="n">
+      <c r="I25" s="18" t="n">
         <v>188760</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>8809975194439</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr"/>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr"/>
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>CELIMAX DERMA NATURE RELIEF MADECICA PH BALANCING FOAM CLEANSING 150ML</t>
         </is>
       </c>
-      <c r="D26" s="15" t="n">
+      <c r="D26" s="18" t="n">
         <v>488</v>
       </c>
-      <c r="E26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="15" t="n">
+      <c r="E26" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="18" t="n">
         <v>320</v>
       </c>
-      <c r="G26" s="15" t="n"/>
-      <c r="H26" s="15" t="n">
+      <c r="G26" s="18" t="n"/>
+      <c r="H26" s="18" t="n">
         <v>320</v>
       </c>
-      <c r="I26" s="15" t="n">
+      <c r="I26" s="18" t="n">
         <v>156160</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>8809606850505</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>551392965</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="17" t="inlineStr">
         <is>
           <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
         </is>
       </c>
-      <c r="D27" s="15" t="n">
+      <c r="D27" s="18" t="n">
         <v>924</v>
       </c>
-      <c r="E27" s="15" t="n">
+      <c r="E27" s="18" t="n">
         <v>112</v>
       </c>
-      <c r="F27" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="15" t="n"/>
-      <c r="H27" s="15" t="n">
+      <c r="F27" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="18" t="n"/>
+      <c r="H27" s="18" t="n">
         <v>112</v>
       </c>
-      <c r="I27" s="15" t="n">
+      <c r="I27" s="18" t="n">
         <v>103488</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>8809875907412</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>551482493</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]/Сыворотка для выравнивания тона и рельефа кожи лица</t>
         </is>
       </c>
-      <c r="D28" s="15" t="n">
+      <c r="D28" s="18" t="n">
         <v>748</v>
       </c>
-      <c r="E28" s="15" t="n">
+      <c r="E28" s="18" t="n">
         <v>76</v>
       </c>
-      <c r="F28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="15" t="n"/>
-      <c r="H28" s="15" t="n">
+      <c r="F28" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="18" t="n"/>
+      <c r="H28" s="18" t="n">
         <v>76</v>
       </c>
-      <c r="I28" s="15" t="n">
+      <c r="I28" s="18" t="n">
         <v>56848</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>8809875907795</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>551472457</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C29" s="17" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]/Восстанавливающая сыворотка с экстрактом нони для лица</t>
         </is>
       </c>
-      <c r="D29" s="15" t="n">
+      <c r="D29" s="18" t="n">
         <v>824</v>
       </c>
-      <c r="E29" s="15" t="n">
+      <c r="E29" s="18" t="n">
         <v>35</v>
       </c>
-      <c r="F29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="15" t="n"/>
-      <c r="H29" s="15" t="n">
+      <c r="F29" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="18" t="n"/>
+      <c r="H29" s="18" t="n">
         <v>35</v>
       </c>
-      <c r="I29" s="15" t="n">
+      <c r="I29" s="18" t="n">
         <v>28840</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>8809954940132</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>551518955</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C30" s="17" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]/Восстанавливающий тонер с экстрактом нони</t>
         </is>
       </c>
-      <c r="D30" s="15" t="n">
+      <c r="D30" s="18" t="n">
         <v>780</v>
       </c>
-      <c r="E30" s="15" t="n">
+      <c r="E30" s="18" t="n">
         <v>23</v>
       </c>
-      <c r="F30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="15" t="n"/>
-      <c r="H30" s="15" t="n">
+      <c r="F30" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="18" t="n"/>
+      <c r="H30" s="18" t="n">
         <v>23</v>
       </c>
-      <c r="I30" s="15" t="n">
+      <c r="I30" s="18" t="n">
         <v>17940</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="n"/>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="17" t="inlineStr">
+      <c r="A31" s="19" t="n"/>
+      <c r="B31" s="19" t="n"/>
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="18" t="n">
+      <c r="D31" s="19" t="n"/>
+      <c r="E31" s="21" t="n">
         <v>25113</v>
       </c>
-      <c r="F31" s="18" t="n">
+      <c r="F31" s="21" t="n">
         <v>20071</v>
       </c>
-      <c r="G31" s="18" t="n">
+      <c r="G31" s="21" t="n">
         <v>15000</v>
       </c>
-      <c r="H31" s="18" t="n">
+      <c r="H31" s="21" t="n">
         <v>45184</v>
       </c>
-      <c r="I31" s="18" t="n">
+      <c r="I31" s="21" t="n">
         <v>34718177</v>
       </c>
     </row>
@@ -4984,208 +5025,208 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>VT COSMETIC — площадка: OZON</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="22" t="inlineStr">
+      <c r="D3" s="25" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="25" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="22" t="inlineStr">
-        <is>
-          <t>В пути</t>
-        </is>
-      </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="F3" s="25" t="inlineStr">
+        <is>
+          <t>Приход 12.10</t>
+        </is>
+      </c>
+      <c r="G3" s="25" t="inlineStr">
         <is>
           <t>Бишкек</t>
         </is>
       </c>
-      <c r="H3" s="22" t="inlineStr">
+      <c r="H3" s="25" t="inlineStr">
         <is>
           <t>Итого РФ</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="25" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>8803463004286</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>1119249556</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="18" t="n">
         <v>1396</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="18" t="n">
         <v>892</v>
       </c>
-      <c r="F4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n">
+      <c r="F4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="n">
         <v>892</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="18" t="n">
         <v>1245232</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>8803463006501</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr"/>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr"/>
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>VT REEDLE S LIP PLUMPER EXPERT</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="18" t="n">
         <v>751</v>
       </c>
-      <c r="E5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="15" t="n">
+      <c r="E5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="18" t="n">
         <v>528</v>
       </c>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="15" t="n">
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="n">
         <v>528</v>
       </c>
-      <c r="I5" s="15" t="n">
+      <c r="I5" s="18" t="n">
         <v>396528</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>8809695678363</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>1123494802</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="18" t="n">
         <v>1034</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="18" t="n">
         <v>378</v>
       </c>
-      <c r="F6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="15" t="n">
+      <c r="F6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="18" t="n">
         <v>378</v>
       </c>
-      <c r="I6" s="15" t="n">
+      <c r="I6" s="18" t="n">
         <v>390852</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>8809695679544</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr"/>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>VT REEDLE SHOT LIFTING EYE CREAM</t>
         </is>
       </c>
-      <c r="D7" s="20" t="n"/>
-      <c r="E7" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="20" t="n">
+      <c r="D7" s="23" t="n"/>
+      <c r="E7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="23" t="n">
         <v>1056</v>
       </c>
-      <c r="G7" s="15" t="n"/>
-      <c r="H7" s="20" t="n">
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="23" t="n">
         <v>1056</v>
       </c>
-      <c r="I7" s="20" t="n"/>
+      <c r="I7" s="23" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="n"/>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="A8" s="19" t="n"/>
+      <c r="B8" s="19" t="n"/>
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="18" t="n">
+      <c r="D8" s="19" t="n"/>
+      <c r="E8" s="21" t="n">
         <v>1270</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="21" t="n">
         <v>1584</v>
       </c>
-      <c r="G8" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="18" t="n">
+      <c r="G8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="21" t="n">
         <v>2854</v>
       </c>
-      <c r="I8" s="18" t="n">
+      <c r="I8" s="21" t="n">
         <v>2032612</v>
       </c>
     </row>
@@ -5208,262 +5249,262 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>MEDICUBE — площадка: OZON</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="22" t="inlineStr">
+      <c r="D3" s="25" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="25" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="22" t="inlineStr">
-        <is>
-          <t>В пути</t>
-        </is>
-      </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="F3" s="25" t="inlineStr">
+        <is>
+          <t>Приход 12.10</t>
+        </is>
+      </c>
+      <c r="G3" s="25" t="inlineStr">
         <is>
           <t>Бишкек</t>
         </is>
       </c>
-      <c r="H3" s="22" t="inlineStr">
+      <c r="H3" s="25" t="inlineStr">
         <is>
           <t>Итого РФ</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="25" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>8800256115549</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr"/>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr"/>
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>PDRN PINK EXOSOME SHOT SERUM 7500 30ml</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="18" t="n">
         <v>1150</v>
       </c>
-      <c r="E4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="15" t="n">
+      <c r="E4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="18" t="n">
         <v>400</v>
       </c>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n">
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="n">
         <v>400</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="18" t="n">
         <v>460000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>8800256115532</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr"/>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr"/>
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>PDRN PINK EXOSOME SHOT SERUM 2000 30ml</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="18" t="n">
         <v>1050</v>
       </c>
-      <c r="E5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="15" t="n">
+      <c r="E5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="15" t="n">
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I5" s="15" t="n">
+      <c r="I5" s="18" t="n">
         <v>315000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>8800256119660</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr"/>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr"/>
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>TXA NIACINAMIDE CAPSULE CREAM 55g</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="18" t="n">
         <v>1266</v>
       </c>
-      <c r="E6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="15" t="n">
+      <c r="E6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="18" t="n">
         <v>240</v>
       </c>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="15" t="n">
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="18" t="n">
         <v>240</v>
       </c>
-      <c r="I6" s="15" t="n">
+      <c r="I6" s="18" t="n">
         <v>303840</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>8800256108053</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr"/>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr"/>
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>PDRN PINK PEPTIDE SERUM 30ml</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="18" t="n">
         <v>942</v>
       </c>
-      <c r="E7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="15" t="n">
+      <c r="E7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="18" t="n">
         <v>320</v>
       </c>
-      <c r="G7" s="15" t="n"/>
-      <c r="H7" s="15" t="n">
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="18" t="n">
         <v>320</v>
       </c>
-      <c r="I7" s="15" t="n">
+      <c r="I7" s="18" t="n">
         <v>301440</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>8800256118885</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr"/>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr"/>
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>PDRN PINK COLLAGEN CAPSULE CREAM 55g</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="18" t="n">
         <v>1393</v>
       </c>
-      <c r="E8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="15" t="n">
+      <c r="E8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="18" t="n">
         <v>160</v>
       </c>
-      <c r="G8" s="15" t="n"/>
-      <c r="H8" s="15" t="n">
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="18" t="n">
         <v>160</v>
       </c>
-      <c r="I8" s="15" t="n">
+      <c r="I8" s="18" t="n">
         <v>222880</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>8800256113101</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr"/>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr"/>
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>PDRN PINK HYALURONIC MOISTURIZING CREAM 50ml</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="18" t="n">
         <v>936</v>
       </c>
-      <c r="E9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="15" t="n">
+      <c r="E9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="G9" s="15" t="n"/>
-      <c r="H9" s="15" t="n">
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="I9" s="15" t="n">
+      <c r="I9" s="18" t="n">
         <v>187200</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n"/>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="A10" s="19" t="n"/>
+      <c r="B10" s="19" t="n"/>
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="18" t="n">
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="21" t="n">
         <v>1620</v>
       </c>
-      <c r="G10" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="18" t="n">
+      <c r="G10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="21" t="n">
         <v>1620</v>
       </c>
-      <c r="I10" s="18" t="n">
+      <c r="I10" s="21" t="n">
         <v>1790360</v>
       </c>
     </row>
@@ -5486,291 +5527,291 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>DERMA FACTORY — площадка: OZON</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="22" t="inlineStr">
+      <c r="D3" s="25" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="25" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="22" t="inlineStr">
-        <is>
-          <t>В пути</t>
-        </is>
-      </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="F3" s="25" t="inlineStr">
+        <is>
+          <t>Приход 12.10</t>
+        </is>
+      </c>
+      <c r="G3" s="25" t="inlineStr">
         <is>
           <t>Бишкек</t>
         </is>
       </c>
-      <c r="H3" s="22" t="inlineStr">
+      <c r="H3" s="25" t="inlineStr">
         <is>
           <t>Итого РФ</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="25" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>8809331319360</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr"/>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr"/>
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>[Derma Factory] PDRN 4% Ampoule</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="18" t="n">
         <v>592</v>
       </c>
-      <c r="E4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="15" t="n">
+      <c r="E4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="18" t="n">
         <v>1530</v>
       </c>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n">
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="n">
         <v>1530</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="18" t="n">
         <v>905760</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>8809563067923</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr"/>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr"/>
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>[Derma Factory] Porphyrin 20% Ampoule stick</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="18" t="n">
         <v>534</v>
       </c>
-      <c r="E5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="15" t="n">
+      <c r="E5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="18" t="n">
         <v>1053</v>
       </c>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="15" t="n">
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="n">
         <v>1053</v>
       </c>
-      <c r="I5" s="15" t="n">
+      <c r="I5" s="18" t="n">
         <v>562302</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>8809563066773</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr"/>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr"/>
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>[Derma Factory] Retinal 300ppm Cream</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="18" t="n">
         <v>443</v>
       </c>
-      <c r="E6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="15" t="n">
+      <c r="E6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="18" t="n">
         <v>1248</v>
       </c>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="15" t="n">
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="18" t="n">
         <v>1248</v>
       </c>
-      <c r="I6" s="15" t="n">
+      <c r="I6" s="18" t="n">
         <v>552864</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>8809563068258</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr"/>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr"/>
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>[Derma Factory] Tranexamic Acid 6% Cream</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="18" t="n">
         <v>401</v>
       </c>
-      <c r="E7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="15" t="n">
+      <c r="E7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="18" t="n">
         <v>1344</v>
       </c>
-      <c r="G7" s="15" t="n"/>
-      <c r="H7" s="15" t="n">
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="18" t="n">
         <v>1344</v>
       </c>
-      <c r="I7" s="15" t="n">
+      <c r="I7" s="18" t="n">
         <v>538944</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>8809563066797</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr"/>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr"/>
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>[Derma Factory] Niacinamide 20% Serum</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="18" t="n">
         <v>289</v>
       </c>
-      <c r="E8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="15" t="n">
+      <c r="E8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="18" t="n">
         <v>1020</v>
       </c>
-      <c r="G8" s="15" t="n"/>
-      <c r="H8" s="15" t="n">
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="18" t="n">
         <v>1020</v>
       </c>
-      <c r="I8" s="15" t="n">
+      <c r="I8" s="18" t="n">
         <v>294780</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>8809331317182</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr"/>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr"/>
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>[Derma Factory] Matrixyl 15% + Argireline 2% Serum</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="18" t="n">
         <v>684</v>
       </c>
-      <c r="E9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="15" t="n">
+      <c r="E9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="18" t="n">
         <v>420</v>
       </c>
-      <c r="G9" s="15" t="n"/>
-      <c r="H9" s="15" t="n">
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="n">
         <v>420</v>
       </c>
-      <c r="I9" s="15" t="n">
+      <c r="I9" s="18" t="n">
         <v>287280</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>8809331313818</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr"/>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr"/>
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>[Derma Factory] Bakuchiol Spicule Cream</t>
         </is>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="18" t="n">
         <v>455</v>
       </c>
-      <c r="E10" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="15" t="n">
+      <c r="E10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="18" t="n">
         <v>480</v>
       </c>
-      <c r="G10" s="15" t="n"/>
-      <c r="H10" s="15" t="n">
+      <c r="G10" s="18" t="n"/>
+      <c r="H10" s="18" t="n">
         <v>480</v>
       </c>
-      <c r="I10" s="15" t="n">
+      <c r="I10" s="18" t="n">
         <v>218400</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="n"/>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="A11" s="19" t="n"/>
+      <c r="B11" s="19" t="n"/>
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="18" t="n">
+      <c r="D11" s="19" t="n"/>
+      <c r="E11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="21" t="n">
         <v>7095</v>
       </c>
-      <c r="G11" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="18" t="n">
+      <c r="G11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="21" t="n">
         <v>7095</v>
       </c>
-      <c r="I11" s="18" t="n">
+      <c r="I11" s="21" t="n">
         <v>3360330</v>
       </c>
     </row>
@@ -5793,183 +5834,183 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>DEOPROCE — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>В пути</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Приход 12.10</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>Бишкек</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>Итого РФ</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr"/>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr"/>
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>214305722</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>DEOPROCE SHAMPOO+BALSAM - BLACK GARLIC[2000ml]</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="18" t="n">
         <v>787</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="18" t="n">
         <v>352</v>
       </c>
-      <c r="F4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n">
+      <c r="F4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="n">
         <v>352</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="18" t="n">
         <v>277024</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>8809410033545</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>608841921</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [200ml]/ Шампунь с черным чесноком против выпадения волос</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="18" t="n">
         <v>211</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="18" t="n">
         <v>292</v>
       </c>
-      <c r="F5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="15" t="n">
+      <c r="F5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="n">
         <v>292</v>
       </c>
-      <c r="I5" s="15" t="n">
+      <c r="I5" s="18" t="n">
         <v>61612</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>8809975191773</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>608837066</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [600ml] мягкая упаковка Шампунь с черным чесноком против выпадения волос</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="18" t="n">
         <v>330</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="18" t="n">
         <v>55</v>
       </c>
-      <c r="F6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="15" t="n">
+      <c r="F6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="18" t="n">
         <v>55</v>
       </c>
-      <c r="I6" s="15" t="n">
+      <c r="I6" s="18" t="n">
         <v>18150</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n"/>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="A7" s="19" t="n"/>
+      <c r="B7" s="19" t="n"/>
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="18" t="n">
+      <c r="D7" s="19" t="n"/>
+      <c r="E7" s="21" t="n">
         <v>699</v>
       </c>
-      <c r="F7" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="18" t="n">
+      <c r="F7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="21" t="n">
         <v>699</v>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="21" t="n">
         <v>356786</v>
       </c>
     </row>
@@ -5992,154 +6033,154 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>ELIZAVECCA — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>В пути</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Приход 12.10</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>Бишкек</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>Итого РФ</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>8809339903523</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>207796350</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>ELIZAVECCA - CER-100 Collagen Ceramide Coating Protein Treatment [100ml] / Коллагеновая маска для волос</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="18" t="n">
         <v>302</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="18" t="n">
         <v>319</v>
       </c>
-      <c r="F4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n">
+      <c r="F4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="n">
         <v>319</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="18" t="n">
         <v>96338</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>8809418752400</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>206058262</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>ELIZAVECCA - Hell-Pore Galactomyces Pure Ample / Сыворотка для лица с экстрактом галактомисиса</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="18" t="n">
         <v>508</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="18" t="n">
         <v>50</v>
       </c>
-      <c r="F5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="15" t="n">
+      <c r="F5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="n">
         <v>50</v>
       </c>
-      <c r="I5" s="15" t="n">
+      <c r="I5" s="18" t="n">
         <v>25400</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n"/>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="A6" s="19" t="n"/>
+      <c r="B6" s="19" t="n"/>
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="18" t="n">
+      <c r="D6" s="19" t="n"/>
+      <c r="E6" s="21" t="n">
         <v>369</v>
       </c>
-      <c r="F6" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="18" t="n">
+      <c r="F6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="21" t="n">
         <v>369</v>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="21" t="n">
         <v>121738</v>
       </c>
     </row>
@@ -6162,571 +6203,571 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>ENOUGH — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>В пути</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Приход 12.10</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>Бишкек</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>Итого РФ</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>8809755463335</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>238415286</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="18" t="n">
         <v>221</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="18" t="n">
         <v>5314</v>
       </c>
-      <c r="F4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n">
+      <c r="F4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="n">
         <v>5314</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="18" t="n">
         <v>1174394</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>8809605870993</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>170198835</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>ENOUGH - Premium Ultra X10 Cover Up Collagen Foundation [Tone 13] / Тональный крем с коллагеном 13 тон</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="18" t="n">
         <v>375</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="18" t="n">
         <v>908</v>
       </c>
-      <c r="F5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="15" t="n">
+      <c r="F5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="n">
         <v>908</v>
       </c>
-      <c r="I5" s="15" t="n">
+      <c r="I5" s="18" t="n">
         <v>340500</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr"/>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr"/>
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>212889028</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="18" t="n">
         <v>243</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="18" t="n">
         <v>682</v>
       </c>
-      <c r="F6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="15" t="n">
+      <c r="F6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="18" t="n">
         <v>682</v>
       </c>
-      <c r="I6" s="15" t="n">
+      <c r="I6" s="18" t="n">
         <v>165726</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>8809755462116</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>238413828</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>ENOUGH - Collagen Moisture BB Cream SPF47 PA+++ [50ml] / Увлажняющий BB крем с коллагеном</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="18" t="n">
         <v>249</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="18" t="n">
         <v>664</v>
       </c>
-      <c r="F7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="15" t="n"/>
-      <c r="H7" s="15" t="n">
+      <c r="F7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="18" t="n">
         <v>664</v>
       </c>
-      <c r="I7" s="15" t="n">
+      <c r="I7" s="18" t="n">
         <v>165336</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>8809474498809</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>207796789</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>ENOUGH - Gold Snail Moisture Foundation [Tone 13] / Тональный крем с муцином улитки 13 тон</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="18" t="n">
         <v>306</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="18" t="n">
         <v>457</v>
       </c>
-      <c r="F8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="15" t="n"/>
-      <c r="H8" s="15" t="n">
+      <c r="F8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="18" t="n">
         <v>457</v>
       </c>
-      <c r="I8" s="15" t="n">
+      <c r="I8" s="18" t="n">
         <v>139842</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>8809605871945</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>170198109</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>ENOUGH - Premium Rich Gold Double Wear Radiance Foundation [Tone 21] / Тональный крем с частичками золота 21 тон</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="18" t="n">
         <v>330</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="18" t="n">
         <v>338</v>
       </c>
-      <c r="F9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="15" t="n"/>
-      <c r="H9" s="15" t="n">
+      <c r="F9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="n">
         <v>338</v>
       </c>
-      <c r="I9" s="15" t="n">
+      <c r="I9" s="18" t="n">
         <v>111540</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr"/>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr"/>
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>212889027</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
         </is>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="18" t="n">
         <v>243</v>
       </c>
-      <c r="E10" s="15" t="n">
+      <c r="E10" s="18" t="n">
         <v>454</v>
       </c>
-      <c r="F10" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="15" t="n"/>
-      <c r="H10" s="15" t="n">
+      <c r="F10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="18" t="n"/>
+      <c r="H10" s="18" t="n">
         <v>454</v>
       </c>
-      <c r="I10" s="15" t="n">
+      <c r="I10" s="18" t="n">
         <v>110322</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr"/>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr"/>
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>212889025</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) 4.5 рейтинг</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="18" t="n">
         <v>243</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="18" t="n">
         <v>289</v>
       </c>
-      <c r="F11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="15" t="n"/>
-      <c r="H11" s="15" t="n">
+      <c r="F11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="18" t="n"/>
+      <c r="H11" s="18" t="n">
         <v>289</v>
       </c>
-      <c r="I11" s="15" t="n">
+      <c r="I11" s="18" t="n">
         <v>70227</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>8809474498816</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>207796898</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>ENOUGH - Gold Snail Moisture Foundation [Tone 21] / Тональный крем с муцином улитки 21 тон</t>
         </is>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="18" t="n">
         <v>331</v>
       </c>
-      <c r="E12" s="15" t="n">
+      <c r="E12" s="18" t="n">
         <v>186</v>
       </c>
-      <c r="F12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="15" t="n"/>
-      <c r="H12" s="15" t="n">
+      <c r="F12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="n">
         <v>186</v>
       </c>
-      <c r="I12" s="15" t="n">
+      <c r="I12" s="18" t="n">
         <v>61566</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>8809605871938</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>170198180</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>ENOUGH - Premium Rich Gold Double Wear Radiance Foundation [Tone 13] / Тональный крем с частичками золота 13 тон</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="18" t="n">
         <v>330</v>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E13" s="18" t="n">
         <v>133</v>
       </c>
-      <c r="F13" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="15" t="n"/>
-      <c r="H13" s="15" t="n">
+      <c r="F13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="18" t="n"/>
+      <c r="H13" s="18" t="n">
         <v>133</v>
       </c>
-      <c r="I13" s="15" t="n">
+      <c r="I13" s="18" t="n">
         <v>43890</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>8809480652165</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>238416010</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
         </is>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="18" t="n">
         <v>244</v>
       </c>
-      <c r="E14" s="15" t="n">
+      <c r="E14" s="18" t="n">
         <v>158</v>
       </c>
-      <c r="F14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="15" t="n"/>
-      <c r="H14" s="15" t="n">
+      <c r="F14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="18" t="n">
         <v>158</v>
       </c>
-      <c r="I14" s="15" t="n">
+      <c r="I14" s="18" t="n">
         <v>38552</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>8809280062379</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>150925322</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>ENOUGH - Collagen Moisture Foundation [Tone 21] / Тональный крем для лица с коллагеном 21 тон</t>
         </is>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D15" s="18" t="n">
         <v>303</v>
       </c>
-      <c r="E15" s="15" t="n">
+      <c r="E15" s="18" t="n">
         <v>126</v>
       </c>
-      <c r="F15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="15" t="n"/>
-      <c r="H15" s="15" t="n">
+      <c r="F15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="18" t="n">
         <v>126</v>
       </c>
-      <c r="I15" s="15" t="n">
+      <c r="I15" s="18" t="n">
         <v>38178</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>8809605870979</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>170198337</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>ENOUGH - Premium 8 Peptide Full Cover Perfect Foundation [Tone 21] / Тональный крем с пептидами 21 тон</t>
         </is>
       </c>
-      <c r="D16" s="15" t="n">
+      <c r="D16" s="18" t="n">
         <v>365</v>
       </c>
-      <c r="E16" s="15" t="n">
+      <c r="E16" s="18" t="n">
         <v>17</v>
       </c>
-      <c r="F16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="15" t="n"/>
-      <c r="H16" s="15" t="n">
+      <c r="F16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="18" t="n">
         <v>17</v>
       </c>
-      <c r="I16" s="15" t="n">
+      <c r="I16" s="18" t="n">
         <v>6205</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>8809280062362</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>150925321</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>ENOUGH - Collagen Moisture Foundation [Tone 13] / Тональный крем для лица с коллагеном 13 тон</t>
         </is>
       </c>
-      <c r="D17" s="15" t="n">
+      <c r="D17" s="18" t="n">
         <v>276</v>
       </c>
-      <c r="E17" s="15" t="n">
+      <c r="E17" s="18" t="n">
         <v>17</v>
       </c>
-      <c r="F17" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="15" t="n"/>
-      <c r="H17" s="15" t="n">
+      <c r="F17" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="18" t="n"/>
+      <c r="H17" s="18" t="n">
         <v>17</v>
       </c>
-      <c r="I17" s="15" t="n">
+      <c r="I17" s="18" t="n">
         <v>4692</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>8809474497079</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>151132052</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>ENOUGH - Collagen 3in1 Whitening Moisture Foundation [Tone 21] / Тональный крем для лица с коллагеном 3в1 [21 тон]</t>
         </is>
       </c>
-      <c r="D18" s="15" t="n">
+      <c r="D18" s="18" t="n">
         <v>283</v>
       </c>
-      <c r="E18" s="15" t="n">
+      <c r="E18" s="18" t="n">
         <v>12</v>
       </c>
-      <c r="F18" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="15" t="n"/>
-      <c r="H18" s="15" t="n">
+      <c r="F18" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="18" t="n"/>
+      <c r="H18" s="18" t="n">
         <v>12</v>
       </c>
-      <c r="I18" s="15" t="n">
+      <c r="I18" s="18" t="n">
         <v>3396</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="n"/>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="A19" s="19" t="n"/>
+      <c r="B19" s="19" t="n"/>
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="18" t="n">
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="21" t="n">
         <v>9755</v>
       </c>
-      <c r="F19" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="18" t="n">
+      <c r="F19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="21" t="n">
         <v>9755</v>
       </c>
-      <c r="I19" s="18" t="n">
+      <c r="I19" s="21" t="n">
         <v>2474366</v>
       </c>
     </row>
@@ -6749,121 +6790,121 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>ETUDE — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>В пути</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Приход 12.10</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>Бишкек</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>Итого РФ</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>8809820683118</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>151313163</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="18" t="n">
         <v>421</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="18" t="n">
         <v>6962</v>
       </c>
-      <c r="F4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n">
+      <c r="F4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="n">
         <v>6962</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="18" t="n">
         <v>2931002</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="A5" s="19" t="n"/>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="18" t="n">
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="21" t="n">
         <v>6962</v>
       </c>
-      <c r="F5" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="18" t="n">
+      <c r="F5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="21" t="n">
         <v>6962</v>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="I5" s="21" t="n">
         <v>2931002</v>
       </c>
     </row>
@@ -6886,418 +6927,418 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>FARMSTAY — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>В пути</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Приход 12.10</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>Бишкек</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>Итого РФ</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>8809469770002</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>168956391</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="18" t="n">
         <v>408</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="18" t="n">
         <v>5563</v>
       </c>
-      <c r="F4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n">
+      <c r="F4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="n">
         <v>5563</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="18" t="n">
         <v>2269704</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>8809595053284</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>207475898</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер 2в1 с коллагеном</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="18" t="n">
         <v>457</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="18" t="n">
         <v>3287</v>
       </c>
-      <c r="F5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="15" t="n">
+      <c r="F5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="n">
         <v>3287</v>
       </c>
-      <c r="I5" s="15" t="n">
+      <c r="I5" s="18" t="n">
         <v>1502159</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>8809595056384</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>207472742</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="18" t="n">
         <v>457</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="18" t="n">
         <v>3053</v>
       </c>
-      <c r="F6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="15" t="n">
+      <c r="F6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="18" t="n">
         <v>3053</v>
       </c>
-      <c r="I6" s="15" t="n">
+      <c r="I6" s="18" t="n">
         <v>1395221</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>8809595053659</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>207476309</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер с аргановым маслом</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="18" t="n">
         <v>461</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="18" t="n">
         <v>2187</v>
       </c>
-      <c r="F7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="15" t="n"/>
-      <c r="H7" s="15" t="n">
+      <c r="F7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="18" t="n">
         <v>2187</v>
       </c>
-      <c r="I7" s="15" t="n">
+      <c r="I7" s="18" t="n">
         <v>1008207</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>8809480770975</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>207469760</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="18" t="n">
         <v>491</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="18" t="n">
         <v>770</v>
       </c>
-      <c r="F8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="15" t="n"/>
-      <c r="H8" s="15" t="n">
+      <c r="F8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="18" t="n">
         <v>770</v>
       </c>
-      <c r="I8" s="15" t="n">
+      <c r="I8" s="18" t="n">
         <v>378070</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>8809469772778</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>419630142</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой </t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="18" t="n">
         <v>450</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="18" t="n">
         <v>623</v>
       </c>
-      <c r="F9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="15" t="n"/>
-      <c r="H9" s="15" t="n">
+      <c r="F9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="n">
         <v>623</v>
       </c>
-      <c r="I9" s="15" t="n">
+      <c r="I9" s="18" t="n">
         <v>280350</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>8809317289274</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>169076150</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
         </is>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="18" t="n">
         <v>374</v>
       </c>
-      <c r="E10" s="15" t="n">
+      <c r="E10" s="18" t="n">
         <v>512</v>
       </c>
-      <c r="F10" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="15" t="n"/>
-      <c r="H10" s="15" t="n">
+      <c r="F10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="18" t="n"/>
+      <c r="H10" s="18" t="n">
         <v>512</v>
       </c>
-      <c r="I10" s="15" t="n">
+      <c r="I10" s="18" t="n">
         <v>191488</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>8802221001338</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>207477077</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>FARMSTAY - Collagen Water Full Moist Cream [100g] / Увлажняющий крем с коллагеном</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="18" t="n">
         <v>544</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="18" t="n">
         <v>165</v>
       </c>
-      <c r="F11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="15" t="n"/>
-      <c r="H11" s="15" t="n">
+      <c r="F11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="18" t="n"/>
+      <c r="H11" s="18" t="n">
         <v>165</v>
       </c>
-      <c r="I11" s="15" t="n">
+      <c r="I11" s="18" t="n">
         <v>89760</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>8809317289472</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>207476777</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания </t>
         </is>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="18" t="n">
         <v>221</v>
       </c>
-      <c r="E12" s="15" t="n">
+      <c r="E12" s="18" t="n">
         <v>313</v>
       </c>
-      <c r="F12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="15" t="n"/>
-      <c r="H12" s="15" t="n">
+      <c r="F12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="n">
         <v>313</v>
       </c>
-      <c r="I12" s="15" t="n">
+      <c r="I12" s="18" t="n">
         <v>69173</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>8809480772504</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>212885914</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml] / Сыворотка роллер для глаз</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="18" t="n">
         <v>292</v>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E13" s="18" t="n">
         <v>118</v>
       </c>
-      <c r="F13" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="15" t="n"/>
-      <c r="H13" s="15" t="n">
+      <c r="F13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="18" t="n"/>
+      <c r="H13" s="18" t="n">
         <v>118</v>
       </c>
-      <c r="I13" s="15" t="n">
+      <c r="I13" s="18" t="n">
         <v>34456</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n"/>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="A14" s="19" t="n"/>
+      <c r="B14" s="19" t="n"/>
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="18" t="n">
+      <c r="D14" s="19" t="n"/>
+      <c r="E14" s="21" t="n">
         <v>16591</v>
       </c>
-      <c r="F14" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="18" t="n">
+      <c r="F14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="21" t="n">
         <v>16591</v>
       </c>
-      <c r="I14" s="18" t="n">
+      <c r="I14" s="21" t="n">
         <v>7218588</v>
       </c>
     </row>
@@ -7320,121 +7361,121 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>HEIMISH — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>В пути</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Приход 12.10</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>Бишкек</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>Итого РФ</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>8809481760463</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>207466866</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] / База под макияж SPF50+ PA+++</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="18" t="n">
         <v>830</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="18" t="n">
         <v>836</v>
       </c>
-      <c r="F4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n">
+      <c r="F4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="n">
         <v>836</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="18" t="n">
         <v>693880</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="A5" s="19" t="n"/>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="18" t="n">
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="21" t="n">
         <v>836</v>
       </c>
-      <c r="F5" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="18" t="n">
+      <c r="F5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="21" t="n">
         <v>836</v>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="I5" s="21" t="n">
         <v>693880</v>
       </c>
     </row>
@@ -7457,348 +7498,348 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>JIGOTT — площадка: WB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Баркод</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>Остаток склад</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>В пути</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Приход 12.10</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>Бишкек</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>Итого РФ</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>8809210034124</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>207482718</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="18" t="n">
         <v>262</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="18" t="n">
         <v>6937</v>
       </c>
-      <c r="F4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n">
+      <c r="F4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="n">
         <v>6937</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="18" t="n">
         <v>1817494</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr"/>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr"/>
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>255574453</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>JIGOTT - Ассорти набор масок [27ml х 15]</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="18" t="n">
         <v>394</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="18" t="n">
         <v>1160</v>
       </c>
-      <c r="F5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="15" t="n">
+      <c r="F5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="n">
         <v>1160</v>
       </c>
-      <c r="I5" s="15" t="n">
+      <c r="I5" s="18" t="n">
         <v>457040</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>8809210034087</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>207483780</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>JIGOTT - Birds Nest Firming Cream [70ml] / Антивозрастной крем с экстрактом ласточкиного гнезда</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="18" t="n">
         <v>262</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="18" t="n">
         <v>1485</v>
       </c>
-      <c r="F6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="15" t="n">
+      <c r="F6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="18" t="n">
         <v>1485</v>
       </c>
-      <c r="I6" s="15" t="n">
+      <c r="I6" s="18" t="n">
         <v>389070</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>8809541282447</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>212757456</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="18" t="n">
         <v>325</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="18" t="n">
         <v>1154</v>
       </c>
-      <c r="F7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="15" t="n"/>
-      <c r="H7" s="15" t="n">
+      <c r="F7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="18" t="n">
         <v>1154</v>
       </c>
-      <c r="I7" s="15" t="n">
+      <c r="I7" s="18" t="n">
         <v>375050</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>8809541282461</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>212760119</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="18" t="n">
         <v>325</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="18" t="n">
         <v>1124</v>
       </c>
-      <c r="F8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="15" t="n"/>
-      <c r="H8" s="15" t="n">
+      <c r="F8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="18" t="n">
         <v>1124</v>
       </c>
-      <c r="I8" s="15" t="n">
+      <c r="I8" s="18" t="n">
         <v>365300</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>8809210036517</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>207483179</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица увлажняющий антивозрастной с муцином улитки</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="18" t="n">
         <v>246</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="18" t="n">
         <v>524</v>
       </c>
-      <c r="F9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="15" t="n"/>
-      <c r="H9" s="15" t="n">
+      <c r="F9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="n">
         <v>524</v>
       </c>
-      <c r="I9" s="15" t="n">
+      <c r="I9" s="18" t="n">
         <v>128904</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>8809541282485</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>212883090</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>JIGOTT - Aura Secret Hyaluronec Acid Toner [300ml] / Тонер с гиалуроновой кислотой антивозрастной</t>
         </is>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="18" t="n">
         <v>325</v>
       </c>
-      <c r="E10" s="15" t="n">
+      <c r="E10" s="18" t="n">
         <v>92</v>
       </c>
-      <c r="F10" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="15" t="n"/>
-      <c r="H10" s="15" t="n">
+      <c r="F10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="18" t="n"/>
+      <c r="H10" s="18" t="n">
         <v>92</v>
       </c>
-      <c r="I10" s="15" t="n">
+      <c r="I10" s="18" t="n">
         <v>29900</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>8809541282508</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>212759698</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml] / Тонер для лица увлажняющий с экстрактом алоэ</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="18" t="n">
         <v>325</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="18" t="n">
         <v>69</v>
       </c>
-      <c r="F11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="15" t="n"/>
-      <c r="H11" s="15" t="n">
+      <c r="F11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="18" t="n"/>
+      <c r="H11" s="18" t="n">
         <v>69</v>
       </c>
-      <c r="I11" s="15" t="n">
+      <c r="I11" s="18" t="n">
         <v>22425</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n"/>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="A12" s="19" t="n"/>
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="18" t="n">
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="21" t="n">
         <v>12545</v>
       </c>
-      <c r="F12" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="18" t="n">
+      <c r="F12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="21" t="n">
         <v>12545</v>
       </c>
-      <c r="I12" s="18" t="n">
+      <c r="I12" s="21" t="n">
         <v>3585183</v>
       </c>
     </row>

--- a/outputs/остатки_себес_по_брендам_площадки.xlsx
+++ b/outputs/остатки_себес_по_брендам_площадки.xlsx
@@ -578,7 +578,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12.10 машина привозит приход (без 15 000 пенки и 15 000 тонера — они в Бишкеке). OZON: Round Lab, Celimax, VT, Medicube, Derma Factory, Skin1004. Остальные — WB.</t>
+          <t>Машина 12.10: Celimax тонер 10 000 + Round Lab пенка 10 000 (ещё по 15 000 каждой в Бишкеке). OZON: Round Lab, Celimax, VT, Medicube, Derma Factory, Skin1004. Остальные — WB.</t>
         </is>
       </c>
     </row>
@@ -634,16 +634,16 @@
         <v>25113</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>20071</v>
+        <v>20063</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>15000</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>45184</v>
+        <v>45176</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>34718177</v>
+        <v>34711073</v>
       </c>
     </row>
     <row r="6">
@@ -661,16 +661,16 @@
         <v>4579</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>13400</v>
+        <v>13380</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>15000</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>17979</v>
+        <v>17959</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>10966609</v>
+        <v>10955169</v>
       </c>
     </row>
     <row r="7">
@@ -1224,16 +1224,16 @@
         <v>89770</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>48290</v>
+        <v>48262</v>
       </c>
       <c r="E27" s="11" t="n">
         <v>30000</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>138060</v>
+        <v>138032</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>80212340</v>
+        <v>80193796</v>
       </c>
     </row>
     <row r="29">
@@ -1246,13 +1246,13 @@
         <v>31011</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>47090</v>
+        <v>47062</v>
       </c>
       <c r="F29" s="13" t="n">
-        <v>78101</v>
+        <v>78073</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>55664646</v>
+        <v>55646102</v>
       </c>
     </row>
     <row r="30">
@@ -2983,16 +2983,16 @@
         <v>2799</v>
       </c>
       <c r="F4" s="18" t="n">
-        <v>10020</v>
+        <v>10000</v>
       </c>
       <c r="G4" s="26" t="n">
         <v>15000</v>
       </c>
       <c r="H4" s="18" t="n">
-        <v>12819</v>
+        <v>12799</v>
       </c>
       <c r="I4" s="18" t="n">
-        <v>7332468</v>
+        <v>7321028</v>
       </c>
     </row>
     <row r="5">
@@ -3335,16 +3335,16 @@
         <v>4579</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>13400</v>
+        <v>13380</v>
       </c>
       <c r="G16" s="21" t="n">
         <v>15000</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>17979</v>
+        <v>17959</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>10966609</v>
+        <v>10955169</v>
       </c>
     </row>
   </sheetData>
@@ -4179,16 +4179,16 @@
         <v>13908</v>
       </c>
       <c r="F4" s="18" t="n">
-        <v>10008</v>
+        <v>10000</v>
       </c>
       <c r="G4" s="26" t="n">
         <v>15000</v>
       </c>
       <c r="H4" s="18" t="n">
-        <v>23916</v>
+        <v>23908</v>
       </c>
       <c r="I4" s="18" t="n">
-        <v>21237408</v>
+        <v>21230304</v>
       </c>
     </row>
     <row r="5">
@@ -4994,16 +4994,16 @@
         <v>25113</v>
       </c>
       <c r="F31" s="21" t="n">
-        <v>20071</v>
+        <v>20063</v>
       </c>
       <c r="G31" s="21" t="n">
         <v>15000</v>
       </c>
       <c r="H31" s="21" t="n">
-        <v>45184</v>
+        <v>45176</v>
       </c>
       <c r="I31" s="21" t="n">
-        <v>34718177</v>
+        <v>34711073</v>
       </c>
     </row>
   </sheetData>
